--- a/research/traditional_assets/database/data/nigeria/nigeria_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_metals_mining.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1869585540538046</v>
+        <v>0.1864291783916432</v>
       </c>
       <c r="C2">
-        <v>3.56896722751514</v>
+        <v>3.547530501575403</v>
       </c>
       <c r="D2">
-        <v>3.54996722751514</v>
+        <v>3.563330501575403</v>
       </c>
       <c r="E2">
-        <v>-1.45</v>
+        <v>-1.4152</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0348</v>
       </c>
       <c r="G2">
         <v>0.019</v>
@@ -1573,28 +1573,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00175044</v>
       </c>
       <c r="N2">
-        <v>0.2666938775510204</v>
+        <v>0.2649434375510204</v>
       </c>
       <c r="O2">
-        <v>0.08000816326530612</v>
+        <v>0.07948303126530612</v>
       </c>
       <c r="P2">
-        <v>0.1866857142857143</v>
+        <v>0.1854604062857143</v>
       </c>
       <c r="Q2">
-        <v>0.2546857142857143</v>
+        <v>0.2534604062857143</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1869585540538046</v>
+        <v>0.1879566448400437</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.9911790399368686</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>152.3581942545991</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1864291783916432</v>
+        <v>0.1858998027294818</v>
       </c>
       <c r="C3">
-        <v>3.547530501575403</v>
+        <v>3.526194763530246</v>
       </c>
       <c r="D3">
-        <v>3.563330501575403</v>
+        <v>3.576794763530246</v>
       </c>
       <c r="E3">
-        <v>-1.4152</v>
+        <v>-1.3804</v>
       </c>
       <c r="F3">
-        <v>0.0348</v>
+        <v>0.0696</v>
       </c>
       <c r="G3">
         <v>0.019</v>
@@ -1655,28 +1655,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M3">
-        <v>0.00175044</v>
+        <v>0.00350088</v>
       </c>
       <c r="N3">
-        <v>0.2649434375510204</v>
+        <v>0.2631929975510204</v>
       </c>
       <c r="O3">
-        <v>0.07948303126530612</v>
+        <v>0.07895789926530612</v>
       </c>
       <c r="P3">
-        <v>0.1854604062857143</v>
+        <v>0.1842350982857143</v>
       </c>
       <c r="Q3">
-        <v>0.2534604062857143</v>
+        <v>0.2522350982857143</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1879566448400437</v>
+        <v>0.1889751048260018</v>
       </c>
       <c r="T3">
-        <v>0.9911790399368686</v>
+        <v>0.9982801936833715</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>152.3581942545991</v>
+        <v>76.17909712729956</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1858998027294818</v>
+        <v>0.1853704270673204</v>
       </c>
       <c r="C4">
-        <v>3.526194763530246</v>
+        <v>3.504961162488428</v>
       </c>
       <c r="D4">
-        <v>3.576794763530246</v>
+        <v>3.590361162488428</v>
       </c>
       <c r="E4">
-        <v>-1.3804</v>
+        <v>-1.3456</v>
       </c>
       <c r="F4">
-        <v>0.0696</v>
+        <v>0.1044</v>
       </c>
       <c r="G4">
         <v>0.019</v>
@@ -1737,28 +1737,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M4">
-        <v>0.00350088</v>
+        <v>0.005251319999999999</v>
       </c>
       <c r="N4">
-        <v>0.2631929975510204</v>
+        <v>0.2614425575510204</v>
       </c>
       <c r="O4">
-        <v>0.07895789926530612</v>
+        <v>0.07843276726530612</v>
       </c>
       <c r="P4">
-        <v>0.1842350982857143</v>
+        <v>0.1830097902857143</v>
       </c>
       <c r="Q4">
-        <v>0.2522350982857143</v>
+        <v>0.2510097902857143</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1889751048260018</v>
+        <v>0.1900145639869282</v>
       </c>
       <c r="T4">
-        <v>0.9982801936833715</v>
+        <v>1.005527762971039</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>76.17909712729956</v>
+        <v>50.78606475153304</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1853704270673204</v>
+        <v>0.184841051405159</v>
       </c>
       <c r="C5">
-        <v>3.504961162488428</v>
+        <v>3.483830865058877</v>
       </c>
       <c r="D5">
-        <v>3.590361162488428</v>
+        <v>3.604030865058877</v>
       </c>
       <c r="E5">
-        <v>-1.3456</v>
+        <v>-1.3108</v>
       </c>
       <c r="F5">
-        <v>0.1044</v>
+        <v>0.1392</v>
       </c>
       <c r="G5">
         <v>0.019</v>
@@ -1819,28 +1819,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M5">
-        <v>0.005251319999999999</v>
+        <v>0.007001759999999999</v>
       </c>
       <c r="N5">
-        <v>0.2614425575510204</v>
+        <v>0.2596921175510204</v>
       </c>
       <c r="O5">
-        <v>0.07843276726530612</v>
+        <v>0.07790763526530611</v>
       </c>
       <c r="P5">
-        <v>0.1830097902857143</v>
+        <v>0.1817844822857143</v>
       </c>
       <c r="Q5">
-        <v>0.2510097902857143</v>
+        <v>0.2497844822857143</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1900145639869282</v>
+        <v>0.1910756785470406</v>
       </c>
       <c r="T5">
-        <v>1.005527762971039</v>
+        <v>1.012926323285534</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.78606475153304</v>
+        <v>38.08954856364977</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.184841051405159</v>
+        <v>0.1843116757429976</v>
       </c>
       <c r="C6">
-        <v>3.483830865058877</v>
+        <v>3.462805055685093</v>
       </c>
       <c r="D6">
-        <v>3.604030865058877</v>
+        <v>3.617805055685093</v>
       </c>
       <c r="E6">
-        <v>-1.3108</v>
+        <v>-1.276</v>
       </c>
       <c r="F6">
-        <v>0.1392</v>
+        <v>0.174</v>
       </c>
       <c r="G6">
         <v>0.019</v>
@@ -1901,28 +1901,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M6">
-        <v>0.007001759999999999</v>
+        <v>0.008752199999999998</v>
       </c>
       <c r="N6">
-        <v>0.2596921175510204</v>
+        <v>0.2579416775510204</v>
       </c>
       <c r="O6">
-        <v>0.07790763526530611</v>
+        <v>0.07738250326530613</v>
       </c>
       <c r="P6">
-        <v>0.1817844822857143</v>
+        <v>0.1805591742857143</v>
       </c>
       <c r="Q6">
-        <v>0.2497844822857143</v>
+        <v>0.2485591742857143</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1910756785470406</v>
+        <v>0.1921591323610501</v>
       </c>
       <c r="T6">
-        <v>1.012926323285534</v>
+        <v>1.020480642764544</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.08954856364977</v>
+        <v>30.47163885091982</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1843116757429976</v>
+        <v>0.1837823000808361</v>
       </c>
       <c r="C7">
-        <v>3.462805055685093</v>
+        <v>3.441884936987277</v>
       </c>
       <c r="D7">
-        <v>3.617805055685093</v>
+        <v>3.631684936987277</v>
       </c>
       <c r="E7">
-        <v>-1.276</v>
+        <v>-1.2412</v>
       </c>
       <c r="F7">
-        <v>0.174</v>
+        <v>0.2088</v>
       </c>
       <c r="G7">
         <v>0.019</v>
@@ -1983,28 +1983,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M7">
-        <v>0.008752199999999998</v>
+        <v>0.01050264</v>
       </c>
       <c r="N7">
-        <v>0.2579416775510204</v>
+        <v>0.2561912375510204</v>
       </c>
       <c r="O7">
-        <v>0.07738250326530613</v>
+        <v>0.07685737126530612</v>
       </c>
       <c r="P7">
-        <v>0.1805591742857143</v>
+        <v>0.1793338662857143</v>
       </c>
       <c r="Q7">
-        <v>0.2485591742857143</v>
+        <v>0.2473338662857143</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1921591323610501</v>
+        <v>0.1932656383838682</v>
       </c>
       <c r="T7">
-        <v>1.020480642764544</v>
+        <v>1.028195692445234</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.47163885091982</v>
+        <v>25.39303237576652</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1837823000808361</v>
+        <v>0.1832529244186747</v>
       </c>
       <c r="C8">
-        <v>3.441884936987277</v>
+        <v>3.421071730112342</v>
       </c>
       <c r="D8">
-        <v>3.631684936987277</v>
+        <v>3.645671730112341</v>
       </c>
       <c r="E8">
-        <v>-1.2412</v>
+        <v>-1.2064</v>
       </c>
       <c r="F8">
-        <v>0.2088</v>
+        <v>0.2436</v>
       </c>
       <c r="G8">
         <v>0.019</v>
@@ -2065,28 +2065,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M8">
-        <v>0.01050264</v>
+        <v>0.01225308</v>
       </c>
       <c r="N8">
-        <v>0.2561912375510204</v>
+        <v>0.2544407975510204</v>
       </c>
       <c r="O8">
-        <v>0.07685737126530612</v>
+        <v>0.07633223926530613</v>
       </c>
       <c r="P8">
-        <v>0.1793338662857143</v>
+        <v>0.1781085582857143</v>
       </c>
       <c r="Q8">
-        <v>0.2473338662857143</v>
+        <v>0.2461085582857143</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1932656383838682</v>
+        <v>0.1943959402351342</v>
       </c>
       <c r="T8">
-        <v>1.028195692445234</v>
+        <v>1.036076657172822</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.39303237576652</v>
+        <v>21.76545632208559</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1832529244186747</v>
+        <v>0.1827235487565133</v>
       </c>
       <c r="C9">
-        <v>3.421071730112342</v>
+        <v>3.400366675092064</v>
       </c>
       <c r="D9">
-        <v>3.645671730112341</v>
+        <v>3.659766675092063</v>
       </c>
       <c r="E9">
-        <v>-1.2064</v>
+        <v>-1.1716</v>
       </c>
       <c r="F9">
-        <v>0.2436</v>
+        <v>0.2784</v>
       </c>
       <c r="G9">
         <v>0.019</v>
@@ -2147,28 +2147,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M9">
-        <v>0.01225308</v>
+        <v>0.01400352</v>
       </c>
       <c r="N9">
-        <v>0.2544407975510204</v>
+        <v>0.2526903575510204</v>
       </c>
       <c r="O9">
-        <v>0.07633223926530613</v>
+        <v>0.07580710726530612</v>
       </c>
       <c r="P9">
-        <v>0.1781085582857143</v>
+        <v>0.1768832502857143</v>
       </c>
       <c r="Q9">
-        <v>0.2461085582857143</v>
+        <v>0.2448832502857143</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1943959402351342</v>
+        <v>0.1955508138657754</v>
       </c>
       <c r="T9">
-        <v>1.036076657172822</v>
+        <v>1.044128947220575</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.76545632208559</v>
+        <v>19.04477428182489</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1827235487565133</v>
+        <v>0.1821941730943519</v>
       </c>
       <c r="C10">
-        <v>3.400366675092064</v>
+        <v>3.379771031209557</v>
       </c>
       <c r="D10">
-        <v>3.659766675092063</v>
+        <v>3.673971031209556</v>
       </c>
       <c r="E10">
-        <v>-1.1716</v>
+        <v>-1.1368</v>
       </c>
       <c r="F10">
-        <v>0.2784</v>
+        <v>0.3131999999999999</v>
       </c>
       <c r="G10">
         <v>0.019</v>
@@ -2229,28 +2229,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M10">
-        <v>0.01400352</v>
+        <v>0.01575395999999999</v>
       </c>
       <c r="N10">
-        <v>0.2526903575510204</v>
+        <v>0.2509399175510204</v>
       </c>
       <c r="O10">
-        <v>0.07580710726530612</v>
+        <v>0.07528197526530613</v>
       </c>
       <c r="P10">
-        <v>0.1768832502857143</v>
+        <v>0.1756579422857143</v>
       </c>
       <c r="Q10">
-        <v>0.2448832502857143</v>
+        <v>0.2436579422857143</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1955508138657754</v>
+        <v>0.1967310693344526</v>
       </c>
       <c r="T10">
-        <v>1.044128947220575</v>
+        <v>1.05235821067597</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.04477428182489</v>
+        <v>16.92868825051102</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1821941730943519</v>
+        <v>0.1816647974321905</v>
       </c>
       <c r="C11">
-        <v>3.379771031209557</v>
+        <v>3.359286077374323</v>
       </c>
       <c r="D11">
-        <v>3.673971031209556</v>
+        <v>3.688286077374323</v>
       </c>
       <c r="E11">
-        <v>-1.1368</v>
+        <v>-1.102</v>
       </c>
       <c r="F11">
-        <v>0.3131999999999999</v>
+        <v>0.3479999999999999</v>
       </c>
       <c r="G11">
         <v>0.019</v>
@@ -2311,28 +2311,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M11">
-        <v>0.01575395999999999</v>
+        <v>0.0175044</v>
       </c>
       <c r="N11">
-        <v>0.2509399175510204</v>
+        <v>0.2491894775510204</v>
       </c>
       <c r="O11">
-        <v>0.07528197526530613</v>
+        <v>0.07475684326530613</v>
       </c>
       <c r="P11">
-        <v>0.1756579422857143</v>
+        <v>0.1744326342857143</v>
       </c>
       <c r="Q11">
-        <v>0.2436579422857143</v>
+        <v>0.2424326342857143</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1967310693344526</v>
+        <v>0.1979375527024339</v>
       </c>
       <c r="T11">
-        <v>1.05235821067597</v>
+        <v>1.060770346652597</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.92868825051102</v>
+        <v>15.23581942545991</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1816647974321905</v>
+        <v>0.1811354217700291</v>
       </c>
       <c r="C12">
-        <v>3.359286077374323</v>
+        <v>3.338913112506105</v>
       </c>
       <c r="D12">
-        <v>3.688286077374323</v>
+        <v>3.702713112506105</v>
       </c>
       <c r="E12">
-        <v>-1.102</v>
+        <v>-1.0672</v>
       </c>
       <c r="F12">
-        <v>0.348</v>
+        <v>0.3828</v>
       </c>
       <c r="G12">
         <v>0.019</v>
@@ -2393,28 +2393,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M12">
-        <v>0.0175044</v>
+        <v>0.01925484</v>
       </c>
       <c r="N12">
-        <v>0.2491894775510204</v>
+        <v>0.2474390375510204</v>
       </c>
       <c r="O12">
-        <v>0.07475684326530613</v>
+        <v>0.07423171126530613</v>
       </c>
       <c r="P12">
-        <v>0.1744326342857143</v>
+        <v>0.1732073262857143</v>
       </c>
       <c r="Q12">
-        <v>0.2424326342857143</v>
+        <v>0.2412073262857143</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1979375527024339</v>
+        <v>0.1991711480562125</v>
       </c>
       <c r="T12">
-        <v>1.060770346652597</v>
+        <v>1.069371519392743</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.23581942545991</v>
+        <v>13.85074493223628</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1811354217700291</v>
+        <v>0.1807320461078677</v>
       </c>
       <c r="C13">
-        <v>3.338913112506105</v>
+        <v>3.315182272106315</v>
       </c>
       <c r="D13">
-        <v>3.702713112506105</v>
+        <v>3.713782272106315</v>
       </c>
       <c r="E13">
-        <v>-1.0672</v>
+        <v>-1.0324</v>
       </c>
       <c r="F13">
-        <v>0.3828</v>
+        <v>0.4175999999999999</v>
       </c>
       <c r="G13">
         <v>0.019</v>
@@ -2475,45 +2475,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M13">
-        <v>0.01925484</v>
+        <v>0.02163167999999999</v>
       </c>
       <c r="N13">
-        <v>0.2474390375510204</v>
+        <v>0.2450621975510204</v>
       </c>
       <c r="O13">
-        <v>0.07423171126530613</v>
+        <v>0.07351865926530612</v>
       </c>
       <c r="P13">
-        <v>0.1732073262857143</v>
+        <v>0.1715435382857143</v>
       </c>
       <c r="Q13">
-        <v>0.2412073262857143</v>
+        <v>0.2395435382857143</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1991711480562125</v>
+        <v>0.2004327796680314</v>
       </c>
       <c r="T13">
-        <v>1.069371519392743</v>
+        <v>1.078168173331529</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.85074493223628</v>
+        <v>12.3288564527129</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1807320461078677</v>
+        <v>0.1802131704457062</v>
       </c>
       <c r="C14">
-        <v>3.315182272106315</v>
+        <v>3.294718599634137</v>
       </c>
       <c r="D14">
-        <v>3.713782272106315</v>
+        <v>3.728118599634137</v>
       </c>
       <c r="E14">
-        <v>-1.0324</v>
+        <v>-0.9976</v>
       </c>
       <c r="F14">
-        <v>0.4175999999999999</v>
+        <v>0.4524</v>
       </c>
       <c r="G14">
         <v>0.019</v>
@@ -2557,28 +2557,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M14">
-        <v>0.02163167999999999</v>
+        <v>0.02343432</v>
       </c>
       <c r="N14">
-        <v>0.2450621975510204</v>
+        <v>0.2432595575510204</v>
       </c>
       <c r="O14">
-        <v>0.07351865926530612</v>
+        <v>0.07297786726530613</v>
       </c>
       <c r="P14">
-        <v>0.1715435382857143</v>
+        <v>0.1702816902857143</v>
       </c>
       <c r="Q14">
-        <v>0.2395435382857143</v>
+        <v>0.2382816902857143</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2004327796680314</v>
+        <v>0.2017234143054095</v>
       </c>
       <c r="T14">
-        <v>1.078168173331529</v>
+        <v>1.087167049199942</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.3288564527129</v>
+        <v>11.38048287942729</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1802131704457062</v>
+        <v>0.1796942947835449</v>
       </c>
       <c r="C15">
-        <v>3.294718599634137</v>
+        <v>3.274366041253127</v>
       </c>
       <c r="D15">
-        <v>3.728118599634137</v>
+        <v>3.742566041253127</v>
       </c>
       <c r="E15">
-        <v>-0.9976</v>
+        <v>-0.9628</v>
       </c>
       <c r="F15">
-        <v>0.4524</v>
+        <v>0.4872</v>
       </c>
       <c r="G15">
         <v>0.019</v>
@@ -2639,28 +2639,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M15">
-        <v>0.02343432</v>
+        <v>0.02523696</v>
       </c>
       <c r="N15">
-        <v>0.2432595575510204</v>
+        <v>0.2414569175510204</v>
       </c>
       <c r="O15">
-        <v>0.07297786726530613</v>
+        <v>0.07243707526530613</v>
       </c>
       <c r="P15">
-        <v>0.1702816902857143</v>
+        <v>0.1690198422857143</v>
       </c>
       <c r="Q15">
-        <v>0.2382816902857143</v>
+        <v>0.2370198422857143</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2017234143054095</v>
+        <v>0.2030440637017963</v>
       </c>
       <c r="T15">
-        <v>1.087167049199942</v>
+        <v>1.096375201251341</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.38048287942729</v>
+        <v>10.56759124518248</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1796942947835449</v>
+        <v>0.1791754191213834</v>
       </c>
       <c r="C16">
-        <v>3.274366041253127</v>
+        <v>3.25412589377791</v>
       </c>
       <c r="D16">
-        <v>3.742566041253127</v>
+        <v>3.757125893777909</v>
       </c>
       <c r="E16">
-        <v>-0.9628</v>
+        <v>-0.9279999999999999</v>
       </c>
       <c r="F16">
-        <v>0.4872</v>
+        <v>0.522</v>
       </c>
       <c r="G16">
         <v>0.019</v>
@@ -2721,28 +2721,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M16">
-        <v>0.02523696</v>
+        <v>0.0270396</v>
       </c>
       <c r="N16">
-        <v>0.2414569175510204</v>
+        <v>0.2396542775510204</v>
       </c>
       <c r="O16">
-        <v>0.07243707526530613</v>
+        <v>0.07189628326530613</v>
       </c>
       <c r="P16">
-        <v>0.1690198422857143</v>
+        <v>0.1677579942857143</v>
       </c>
       <c r="Q16">
-        <v>0.2370198422857143</v>
+        <v>0.2357579942857143</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2030440637017963</v>
+        <v>0.2043957872016275</v>
       </c>
       <c r="T16">
-        <v>1.096375201251341</v>
+        <v>1.10580001570395</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.56759124518248</v>
+        <v>9.863085162170314</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1791754191213834</v>
+        <v>0.178846943459222</v>
       </c>
       <c r="C17">
-        <v>3.25412589377791</v>
+        <v>3.228601750732569</v>
       </c>
       <c r="D17">
-        <v>3.757125893777909</v>
+        <v>3.766401750732569</v>
       </c>
       <c r="E17">
-        <v>-0.928</v>
+        <v>-0.8932</v>
       </c>
       <c r="F17">
-        <v>0.5219999999999999</v>
+        <v>0.5568</v>
       </c>
       <c r="G17">
         <v>0.019</v>
@@ -2803,45 +2803,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M17">
-        <v>0.02703959999999999</v>
+        <v>0.0297888</v>
       </c>
       <c r="N17">
-        <v>0.2396542775510204</v>
+        <v>0.2369050775510204</v>
       </c>
       <c r="O17">
-        <v>0.07189628326530613</v>
+        <v>0.07107152326530612</v>
       </c>
       <c r="P17">
-        <v>0.1677579942857143</v>
+        <v>0.1658335542857143</v>
       </c>
       <c r="Q17">
-        <v>0.2357579942857143</v>
+        <v>0.2338335542857143</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2043957872016275</v>
+        <v>0.2057796945943119</v>
       </c>
       <c r="T17">
-        <v>1.10580001570395</v>
+        <v>1.115449230500669</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.863085162170316</v>
+        <v>8.952823797904596</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.178846943459222</v>
+        <v>0.1783399677970606</v>
       </c>
       <c r="C18">
-        <v>3.228601750732569</v>
+        <v>3.208208529708607</v>
       </c>
       <c r="D18">
-        <v>3.766401750732569</v>
+        <v>3.780808529708607</v>
       </c>
       <c r="E18">
-        <v>-0.8932</v>
+        <v>-0.8583999999999999</v>
       </c>
       <c r="F18">
-        <v>0.5568</v>
+        <v>0.5916</v>
       </c>
       <c r="G18">
         <v>0.019</v>
@@ -2885,28 +2885,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M18">
-        <v>0.0297888</v>
+        <v>0.0316506</v>
       </c>
       <c r="N18">
-        <v>0.2369050775510204</v>
+        <v>0.2350432775510204</v>
       </c>
       <c r="O18">
-        <v>0.07107152326530612</v>
+        <v>0.07051298326530613</v>
       </c>
       <c r="P18">
-        <v>0.1658335542857143</v>
+        <v>0.1645302942857143</v>
       </c>
       <c r="Q18">
-        <v>0.2338335542857143</v>
+        <v>0.2325302942857143</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2057796945943119</v>
+        <v>0.2071969491530851</v>
       </c>
       <c r="T18">
-        <v>1.115449230500669</v>
+        <v>1.125330956497308</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.952823797904596</v>
+        <v>8.426187103910207</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1783399677970606</v>
+        <v>0.1778329921348991</v>
       </c>
       <c r="C19">
-        <v>3.208208529708607</v>
+        <v>3.187925945976023</v>
       </c>
       <c r="D19">
-        <v>3.780808529708607</v>
+        <v>3.795325945976022</v>
       </c>
       <c r="E19">
-        <v>-0.8583999999999999</v>
+        <v>-0.8236</v>
       </c>
       <c r="F19">
-        <v>0.5916</v>
+        <v>0.6264</v>
       </c>
       <c r="G19">
         <v>0.019</v>
@@ -2967,28 +2967,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M19">
-        <v>0.0316506</v>
+        <v>0.0335124</v>
       </c>
       <c r="N19">
-        <v>0.2350432775510204</v>
+        <v>0.2331814775510204</v>
       </c>
       <c r="O19">
-        <v>0.07051298326530613</v>
+        <v>0.06995444326530613</v>
       </c>
       <c r="P19">
-        <v>0.1645302942857143</v>
+        <v>0.1632270342857143</v>
       </c>
       <c r="Q19">
-        <v>0.2325302942857143</v>
+        <v>0.2312270342857143</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2071969491530851</v>
+        <v>0.2086487708962185</v>
       </c>
       <c r="T19">
-        <v>1.125330956497308</v>
+        <v>1.135453700201183</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.426187103910207</v>
+        <v>7.958065598137419</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1778329921348992</v>
+        <v>0.1774324164727378</v>
       </c>
       <c r="C20">
-        <v>3.187925945976022</v>
+        <v>3.16467564812893</v>
       </c>
       <c r="D20">
-        <v>3.795325945976022</v>
+        <v>3.80687564812893</v>
       </c>
       <c r="E20">
-        <v>-0.8236000000000001</v>
+        <v>-0.7888000000000001</v>
       </c>
       <c r="F20">
-        <v>0.6263999999999998</v>
+        <v>0.6611999999999999</v>
       </c>
       <c r="G20">
         <v>0.019</v>
@@ -3049,45 +3049,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M20">
-        <v>0.03351239999999999</v>
+        <v>0.03590316</v>
       </c>
       <c r="N20">
-        <v>0.2331814775510204</v>
+        <v>0.2307907175510204</v>
       </c>
       <c r="O20">
-        <v>0.06995444326530613</v>
+        <v>0.06923721526530613</v>
       </c>
       <c r="P20">
-        <v>0.1632270342857143</v>
+        <v>0.1615535022857143</v>
       </c>
       <c r="Q20">
-        <v>0.2312270342857143</v>
+        <v>0.2295535022857143</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2086487708962185</v>
+        <v>0.2101364400897997</v>
       </c>
       <c r="T20">
-        <v>1.135453700201183</v>
+        <v>1.145826388194042</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.95806559813742</v>
+        <v>7.428144975289653</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1774324164727378</v>
+        <v>0.1769310408105764</v>
       </c>
       <c r="C21">
-        <v>3.16467564812893</v>
+        <v>3.144431124750243</v>
       </c>
       <c r="D21">
-        <v>3.80687564812893</v>
+        <v>3.821431124750243</v>
       </c>
       <c r="E21">
-        <v>-0.7888000000000001</v>
+        <v>-0.754</v>
       </c>
       <c r="F21">
-        <v>0.6611999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="G21">
         <v>0.019</v>
@@ -3131,28 +3131,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M21">
-        <v>0.03590316</v>
+        <v>0.0377928</v>
       </c>
       <c r="N21">
-        <v>0.2307907175510204</v>
+        <v>0.2289010775510204</v>
       </c>
       <c r="O21">
-        <v>0.06923721526530613</v>
+        <v>0.06867032326530612</v>
       </c>
       <c r="P21">
-        <v>0.1615535022857143</v>
+        <v>0.1602307542857143</v>
       </c>
       <c r="Q21">
-        <v>0.2295535022857143</v>
+        <v>0.2282307542857143</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2101364400897997</v>
+        <v>0.2116613010132204</v>
       </c>
       <c r="T21">
-        <v>1.145826388194042</v>
+        <v>1.156458393386723</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.428144975289653</v>
+        <v>7.056737726525169</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1769310408105764</v>
+        <v>0.176429665148415</v>
       </c>
       <c r="C22">
-        <v>3.144431124750243</v>
+        <v>3.124298333445902</v>
       </c>
       <c r="D22">
-        <v>3.821431124750243</v>
+        <v>3.836098333445901</v>
       </c>
       <c r="E22">
-        <v>-0.754</v>
+        <v>-0.7192</v>
       </c>
       <c r="F22">
-        <v>0.696</v>
+        <v>0.7308</v>
       </c>
       <c r="G22">
         <v>0.019</v>
@@ -3213,28 +3213,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M22">
-        <v>0.0377928</v>
+        <v>0.03968244</v>
       </c>
       <c r="N22">
-        <v>0.2289010775510204</v>
+        <v>0.2270114375510204</v>
       </c>
       <c r="O22">
-        <v>0.06867032326530612</v>
+        <v>0.06810343126530613</v>
       </c>
       <c r="P22">
-        <v>0.1602307542857143</v>
+        <v>0.1589080062857143</v>
       </c>
       <c r="Q22">
-        <v>0.2282307542857143</v>
+        <v>0.2269080062857143</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2116613010132204</v>
+        <v>0.2132247660106519</v>
       </c>
       <c r="T22">
-        <v>1.156458393386723</v>
+        <v>1.167359563267826</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.056737726525169</v>
+        <v>6.720702596690638</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1764296651484149</v>
+        <v>0.1759282894862535</v>
       </c>
       <c r="C23">
-        <v>3.124298333445902</v>
+        <v>3.104278565704708</v>
       </c>
       <c r="D23">
-        <v>3.836098333445902</v>
+        <v>3.850878565704708</v>
       </c>
       <c r="E23">
-        <v>-0.7192000000000001</v>
+        <v>-0.6844</v>
       </c>
       <c r="F23">
-        <v>0.7307999999999999</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="G23">
         <v>0.019</v>
@@ -3295,28 +3295,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M23">
-        <v>0.03968243999999999</v>
+        <v>0.04157208</v>
       </c>
       <c r="N23">
-        <v>0.2270114375510204</v>
+        <v>0.2251217975510204</v>
       </c>
       <c r="O23">
-        <v>0.06810343126530613</v>
+        <v>0.06753653926530612</v>
       </c>
       <c r="P23">
-        <v>0.1589080062857143</v>
+        <v>0.1575852582857143</v>
       </c>
       <c r="Q23">
-        <v>0.2269080062857143</v>
+        <v>0.2255852582857143</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2132247660106518</v>
+        <v>0.2148283198541712</v>
       </c>
       <c r="T23">
-        <v>1.167359563267826</v>
+        <v>1.178540250325367</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.720702596690639</v>
+        <v>6.415216115022881</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1759282894862535</v>
+        <v>0.1754269138240921</v>
       </c>
       <c r="C24">
-        <v>3.104278565704708</v>
+        <v>3.084373132996523</v>
       </c>
       <c r="D24">
-        <v>3.850878565704708</v>
+        <v>3.865773132996523</v>
       </c>
       <c r="E24">
-        <v>-0.6844</v>
+        <v>-0.6496000000000001</v>
       </c>
       <c r="F24">
-        <v>0.7655999999999999</v>
+        <v>0.8003999999999999</v>
       </c>
       <c r="G24">
         <v>0.019</v>
@@ -3377,28 +3377,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M24">
-        <v>0.04157208</v>
+        <v>0.04346172</v>
       </c>
       <c r="N24">
-        <v>0.2251217975510204</v>
+        <v>0.2232321575510204</v>
       </c>
       <c r="O24">
-        <v>0.06753653926530612</v>
+        <v>0.06696964726530613</v>
       </c>
       <c r="P24">
-        <v>0.1575852582857143</v>
+        <v>0.1562625102857143</v>
       </c>
       <c r="Q24">
-        <v>0.2255852582857143</v>
+        <v>0.2242625102857143</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2148283198541712</v>
+        <v>0.2164735244468729</v>
       </c>
       <c r="T24">
-        <v>1.178540250325367</v>
+        <v>1.190011344838949</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.415216115022881</v>
+        <v>6.136293675239279</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1754269138240921</v>
+        <v>0.1750935381619307</v>
       </c>
       <c r="C25">
-        <v>3.084373132996523</v>
+        <v>3.059540798019073</v>
       </c>
       <c r="D25">
-        <v>3.865773132996523</v>
+        <v>3.875740798019073</v>
       </c>
       <c r="E25">
-        <v>-0.6496000000000001</v>
+        <v>-0.6148</v>
       </c>
       <c r="F25">
-        <v>0.8003999999999999</v>
+        <v>0.8351999999999999</v>
       </c>
       <c r="G25">
         <v>0.019</v>
@@ -3459,45 +3459,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M25">
-        <v>0.04346172</v>
+        <v>0.04618656</v>
       </c>
       <c r="N25">
-        <v>0.2232321575510204</v>
+        <v>0.2205073175510204</v>
       </c>
       <c r="O25">
-        <v>0.06696964726530613</v>
+        <v>0.06615219526530612</v>
       </c>
       <c r="P25">
-        <v>0.1562625102857143</v>
+        <v>0.1543551222857143</v>
       </c>
       <c r="Q25">
-        <v>0.2242625102857143</v>
+        <v>0.2223551222857143</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2164735244468729</v>
+        <v>0.2181620238972772</v>
       </c>
       <c r="T25">
-        <v>1.190011344838949</v>
+        <v>1.201784310260782</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.136293675239279</v>
+        <v>5.774274541144013</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1750935381619307</v>
+        <v>0.1745991624997693</v>
       </c>
       <c r="C26">
-        <v>3.059540798019073</v>
+        <v>3.039617229559457</v>
       </c>
       <c r="D26">
-        <v>3.875740798019073</v>
+        <v>3.890617229559457</v>
       </c>
       <c r="E26">
-        <v>-0.6148000000000001</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="F26">
-        <v>0.8351999999999998</v>
+        <v>0.8699999999999999</v>
       </c>
       <c r="G26">
         <v>0.019</v>
@@ -3541,28 +3541,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M26">
-        <v>0.04618655999999999</v>
+        <v>0.04811099999999999</v>
       </c>
       <c r="N26">
-        <v>0.2205073175510204</v>
+        <v>0.2185828775510204</v>
       </c>
       <c r="O26">
-        <v>0.06615219526530612</v>
+        <v>0.06557486326530612</v>
       </c>
       <c r="P26">
-        <v>0.1543551222857143</v>
+        <v>0.1530080142857143</v>
       </c>
       <c r="Q26">
-        <v>0.2223551222857143</v>
+        <v>0.2210080142857143</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2181620238972772</v>
+        <v>0.2198955499996924</v>
       </c>
       <c r="T26">
-        <v>1.201784310260782</v>
+        <v>1.213871221427198</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.774274541144013</v>
+        <v>5.543303559498253</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1745991624997693</v>
+        <v>0.1741047868376079</v>
       </c>
       <c r="C27">
-        <v>3.039617229559457</v>
+        <v>3.01980830289731</v>
       </c>
       <c r="D27">
-        <v>3.890617229559457</v>
+        <v>3.905608302897309</v>
       </c>
       <c r="E27">
-        <v>-0.5800000000000001</v>
+        <v>-0.5452</v>
       </c>
       <c r="F27">
-        <v>0.8699999999999999</v>
+        <v>0.9047999999999999</v>
       </c>
       <c r="G27">
         <v>0.019</v>
@@ -3623,28 +3623,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M27">
-        <v>0.04811099999999999</v>
+        <v>0.05003544</v>
       </c>
       <c r="N27">
-        <v>0.2185828775510204</v>
+        <v>0.2166584375510204</v>
       </c>
       <c r="O27">
-        <v>0.06557486326530612</v>
+        <v>0.06499753126530612</v>
       </c>
       <c r="P27">
-        <v>0.1530080142857143</v>
+        <v>0.1516609062857143</v>
       </c>
       <c r="Q27">
-        <v>0.2210080142857143</v>
+        <v>0.2196609062857143</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2198955499996924</v>
+        <v>0.2216759281589296</v>
       </c>
       <c r="T27">
-        <v>1.213871221427198</v>
+        <v>1.226284805868382</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.543303559498253</v>
+        <v>5.330099576440627</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1741047868376079</v>
+        <v>0.1736104111754465</v>
       </c>
       <c r="C28">
-        <v>3.01980830289731</v>
+        <v>3.00011534834948</v>
       </c>
       <c r="D28">
-        <v>3.905608302897309</v>
+        <v>3.920715348349479</v>
       </c>
       <c r="E28">
-        <v>-0.5452</v>
+        <v>-0.5104</v>
       </c>
       <c r="F28">
-        <v>0.9047999999999999</v>
+        <v>0.9396</v>
       </c>
       <c r="G28">
         <v>0.019</v>
@@ -3705,28 +3705,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M28">
-        <v>0.05003544</v>
+        <v>0.05195988</v>
       </c>
       <c r="N28">
-        <v>0.2166584375510204</v>
+        <v>0.2147339975510204</v>
       </c>
       <c r="O28">
-        <v>0.06499753126530612</v>
+        <v>0.06442019926530612</v>
       </c>
       <c r="P28">
-        <v>0.1516609062857143</v>
+        <v>0.1503137982857143</v>
       </c>
       <c r="Q28">
-        <v>0.2196609062857143</v>
+        <v>0.2183137982857143</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2216759281589296</v>
+        <v>0.2235050838019815</v>
       </c>
       <c r="T28">
-        <v>1.226284805868382</v>
+        <v>1.239038488513434</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.330099576440627</v>
+        <v>5.1326884810169</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1736104111754465</v>
+        <v>0.173116035513285</v>
       </c>
       <c r="C29">
-        <v>3.00011534834948</v>
+        <v>2.980539716895612</v>
       </c>
       <c r="D29">
-        <v>3.920715348349479</v>
+        <v>3.935939716895612</v>
       </c>
       <c r="E29">
-        <v>-0.5104</v>
+        <v>-0.4756</v>
       </c>
       <c r="F29">
-        <v>0.9396</v>
+        <v>0.9743999999999999</v>
       </c>
       <c r="G29">
         <v>0.019</v>
@@ -3787,28 +3787,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M29">
-        <v>0.05195988</v>
+        <v>0.05388432</v>
       </c>
       <c r="N29">
-        <v>0.2147339975510204</v>
+        <v>0.2128095575510204</v>
       </c>
       <c r="O29">
-        <v>0.06442019926530612</v>
+        <v>0.06384286726530612</v>
       </c>
       <c r="P29">
-        <v>0.1503137982857143</v>
+        <v>0.1489666902857143</v>
       </c>
       <c r="Q29">
-        <v>0.2183137982857143</v>
+        <v>0.2169666902857143</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2235050838019815</v>
+        <v>0.225385049324007</v>
       </c>
       <c r="T29">
-        <v>1.239038488513434</v>
+        <v>1.252146440120849</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.1326884810169</v>
+        <v>4.94937817812344</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.173116035513285</v>
+        <v>0.1726216598511237</v>
       </c>
       <c r="C30">
-        <v>2.980539716895612</v>
+        <v>2.961082780580884</v>
       </c>
       <c r="D30">
-        <v>3.935939716895612</v>
+        <v>3.951282780580883</v>
       </c>
       <c r="E30">
-        <v>-0.4756</v>
+        <v>-0.4407999999999999</v>
       </c>
       <c r="F30">
-        <v>0.9743999999999999</v>
+        <v>1.0092</v>
       </c>
       <c r="G30">
         <v>0.019</v>
@@ -3869,28 +3869,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M30">
-        <v>0.05388432</v>
+        <v>0.05580876000000001</v>
       </c>
       <c r="N30">
-        <v>0.2128095575510204</v>
+        <v>0.2108851175510204</v>
       </c>
       <c r="O30">
-        <v>0.06384286726530612</v>
+        <v>0.06326553526530612</v>
       </c>
       <c r="P30">
-        <v>0.1489666902857143</v>
+        <v>0.1476195822857143</v>
       </c>
       <c r="Q30">
-        <v>0.2169666902857143</v>
+        <v>0.2156195822857143</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.225385049324007</v>
+        <v>0.2273179716213009</v>
       </c>
       <c r="T30">
-        <v>1.252146440120849</v>
+        <v>1.265623629801712</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.94937817812344</v>
+        <v>4.778709965084699</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1726216598511237</v>
+        <v>0.1721272841889622</v>
       </c>
       <c r="C31">
-        <v>2.961082780580884</v>
+        <v>2.941745932928201</v>
       </c>
       <c r="D31">
-        <v>3.951282780580883</v>
+        <v>3.9667459329282</v>
       </c>
       <c r="E31">
-        <v>-0.4408000000000001</v>
+        <v>-0.4060000000000001</v>
       </c>
       <c r="F31">
-        <v>1.0092</v>
+        <v>1.044</v>
       </c>
       <c r="G31">
         <v>0.019</v>
@@ -3951,28 +3951,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M31">
-        <v>0.05580875999999999</v>
+        <v>0.05773319999999999</v>
       </c>
       <c r="N31">
-        <v>0.2108851175510204</v>
+        <v>0.2089606775510204</v>
       </c>
       <c r="O31">
-        <v>0.06326553526530612</v>
+        <v>0.06268820326530612</v>
       </c>
       <c r="P31">
-        <v>0.1476195822857143</v>
+        <v>0.1462724742857143</v>
       </c>
       <c r="Q31">
-        <v>0.2156195822857143</v>
+        <v>0.2142724742857143</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2273179716213009</v>
+        <v>0.229306120269946</v>
       </c>
       <c r="T31">
-        <v>1.265623629801712</v>
+        <v>1.279485882044885</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.778709965084701</v>
+        <v>4.619419632915211</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1721272841889622</v>
+        <v>0.1721754085268008</v>
       </c>
       <c r="C32">
-        <v>2.941745932928201</v>
+        <v>2.905435377800258</v>
       </c>
       <c r="D32">
-        <v>3.9667459329282</v>
+        <v>3.965235377800257</v>
       </c>
       <c r="E32">
-        <v>-0.4060000000000001</v>
+        <v>-0.3712000000000002</v>
       </c>
       <c r="F32">
-        <v>1.044</v>
+        <v>1.0788</v>
       </c>
       <c r="G32">
         <v>0.019</v>
@@ -4033,45 +4033,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M32">
-        <v>0.05773319999999999</v>
+        <v>0.06235463999999999</v>
       </c>
       <c r="N32">
-        <v>0.2089606775510204</v>
+        <v>0.2043392375510204</v>
       </c>
       <c r="O32">
-        <v>0.06268820326530612</v>
+        <v>0.06130177126530613</v>
       </c>
       <c r="P32">
-        <v>0.1462724742857143</v>
+        <v>0.1430374662857143</v>
       </c>
       <c r="Q32">
-        <v>0.2142724742857143</v>
+        <v>0.2110374662857143</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.229306120269946</v>
+        <v>0.2313518964156533</v>
       </c>
       <c r="T32">
-        <v>1.279485882044885</v>
+        <v>1.293749938700903</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.619419632915211</v>
+        <v>4.277049431301672</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1721754085268008</v>
+        <v>0.1716985328646394</v>
       </c>
       <c r="C33">
-        <v>2.905435377800258</v>
+        <v>2.885654808157301</v>
       </c>
       <c r="D33">
-        <v>3.965235377800257</v>
+        <v>3.980254808157301</v>
       </c>
       <c r="E33">
-        <v>-0.3712000000000002</v>
+        <v>-0.3364</v>
       </c>
       <c r="F33">
-        <v>1.0788</v>
+        <v>1.1136</v>
       </c>
       <c r="G33">
         <v>0.019</v>
@@ -4115,28 +4115,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M33">
-        <v>0.06235463999999999</v>
+        <v>0.06436608000000001</v>
       </c>
       <c r="N33">
-        <v>0.2043392375510204</v>
+        <v>0.2023277975510204</v>
       </c>
       <c r="O33">
-        <v>0.06130177126530613</v>
+        <v>0.06069833926530613</v>
       </c>
       <c r="P33">
-        <v>0.1430374662857143</v>
+        <v>0.1416294582857143</v>
       </c>
       <c r="Q33">
-        <v>0.2110374662857143</v>
+        <v>0.2096294582857143</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2313518964156533</v>
+        <v>0.2334578424479991</v>
       </c>
       <c r="T33">
-        <v>1.293749938700903</v>
+        <v>1.30843352643504</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.277049431301672</v>
+        <v>4.143391636573494</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1716985328646394</v>
+        <v>0.171221657202478</v>
       </c>
       <c r="C34">
-        <v>2.885654808157301</v>
+        <v>2.865988451656739</v>
       </c>
       <c r="D34">
-        <v>3.980254808157301</v>
+        <v>3.995388451656739</v>
       </c>
       <c r="E34">
-        <v>-0.3364</v>
+        <v>-0.3016000000000001</v>
       </c>
       <c r="F34">
-        <v>1.1136</v>
+        <v>1.1484</v>
       </c>
       <c r="G34">
         <v>0.019</v>
@@ -4197,28 +4197,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M34">
-        <v>0.06436608000000001</v>
+        <v>0.06637752</v>
       </c>
       <c r="N34">
-        <v>0.2023277975510204</v>
+        <v>0.2003163575510204</v>
       </c>
       <c r="O34">
-        <v>0.06069833926530613</v>
+        <v>0.06009490726530613</v>
       </c>
       <c r="P34">
-        <v>0.1416294582857143</v>
+        <v>0.1402214502857143</v>
       </c>
       <c r="Q34">
-        <v>0.2096294582857143</v>
+        <v>0.2082214502857143</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2334578424479991</v>
+        <v>0.2356266525410119</v>
       </c>
       <c r="T34">
-        <v>1.30843352643504</v>
+        <v>1.323555430220943</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.143391636573494</v>
+        <v>4.017834314253085</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.171221657202478</v>
+        <v>0.1715777815403165</v>
       </c>
       <c r="C35">
-        <v>2.865988451656739</v>
+        <v>2.819876000050984</v>
       </c>
       <c r="D35">
-        <v>3.995388451656739</v>
+        <v>3.984076000050985</v>
       </c>
       <c r="E35">
-        <v>-0.3016000000000001</v>
+        <v>-0.2667999999999999</v>
       </c>
       <c r="F35">
-        <v>1.1484</v>
+        <v>1.1832</v>
       </c>
       <c r="G35">
         <v>0.019</v>
@@ -4279,45 +4279,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M35">
-        <v>0.06637752</v>
+        <v>0.07253016</v>
       </c>
       <c r="N35">
-        <v>0.2003163575510204</v>
+        <v>0.1941637175510204</v>
       </c>
       <c r="O35">
-        <v>0.06009490726530613</v>
+        <v>0.05824911526530612</v>
       </c>
       <c r="P35">
-        <v>0.1402214502857143</v>
+        <v>0.1359146022857143</v>
       </c>
       <c r="Q35">
-        <v>0.2082214502857143</v>
+        <v>0.2039146022857143</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2356266525410119</v>
+        <v>0.2378611841519948</v>
       </c>
       <c r="T35">
-        <v>1.323555430220943</v>
+        <v>1.339135573515509</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.017834314253085</v>
+        <v>3.677006607334389</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1715777815403165</v>
+        <v>0.1711254058781551</v>
       </c>
       <c r="C36">
-        <v>2.819876000050984</v>
+        <v>2.799456955021732</v>
       </c>
       <c r="D36">
-        <v>3.984076000050985</v>
+        <v>3.998456955021732</v>
       </c>
       <c r="E36">
-        <v>-0.2667999999999999</v>
+        <v>-0.232</v>
       </c>
       <c r="F36">
-        <v>1.1832</v>
+        <v>1.218</v>
       </c>
       <c r="G36">
         <v>0.019</v>
@@ -4361,28 +4361,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M36">
-        <v>0.07253016</v>
+        <v>0.0746634</v>
       </c>
       <c r="N36">
-        <v>0.1941637175510204</v>
+        <v>0.1920304775510204</v>
       </c>
       <c r="O36">
-        <v>0.05824911526530612</v>
+        <v>0.05760914326530613</v>
       </c>
       <c r="P36">
-        <v>0.1359146022857143</v>
+        <v>0.1344213342857143</v>
       </c>
       <c r="Q36">
-        <v>0.2039146022857143</v>
+        <v>0.2024213342857143</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2378611841519948</v>
+        <v>0.2401644705817771</v>
       </c>
       <c r="T36">
-        <v>1.339135573515509</v>
+        <v>1.355195105834523</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.677006607334389</v>
+        <v>3.571949275696264</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1711254058781551</v>
+        <v>0.1713786302159937</v>
       </c>
       <c r="C37">
-        <v>2.799456955021732</v>
+        <v>2.756594224817795</v>
       </c>
       <c r="D37">
-        <v>3.998456955021732</v>
+        <v>3.990394224817795</v>
       </c>
       <c r="E37">
-        <v>-0.232</v>
+        <v>-0.1972</v>
       </c>
       <c r="F37">
-        <v>1.218</v>
+        <v>1.2528</v>
       </c>
       <c r="G37">
         <v>0.019</v>
@@ -4443,45 +4443,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M37">
-        <v>0.0746634</v>
+        <v>0.08030448</v>
       </c>
       <c r="N37">
-        <v>0.1920304775510204</v>
+        <v>0.1863893975510204</v>
       </c>
       <c r="O37">
-        <v>0.05760914326530613</v>
+        <v>0.05591681926530612</v>
       </c>
       <c r="P37">
-        <v>0.1344213342857143</v>
+        <v>0.1304725782857143</v>
       </c>
       <c r="Q37">
-        <v>0.2024213342857143</v>
+        <v>0.1984725782857143</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2401644705817771</v>
+        <v>0.2425397347124902</v>
       </c>
       <c r="T37">
-        <v>1.355195105834523</v>
+        <v>1.371756498538506</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.571949275696264</v>
+        <v>3.321033615447362</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1713786302159938</v>
+        <v>0.1709458545538323</v>
       </c>
       <c r="C38">
-        <v>2.756594224817794</v>
+        <v>2.735593687125895</v>
       </c>
       <c r="D38">
-        <v>3.990394224817794</v>
+        <v>4.004193687125895</v>
       </c>
       <c r="E38">
-        <v>-0.1972000000000003</v>
+        <v>-0.1624000000000001</v>
       </c>
       <c r="F38">
-        <v>1.2528</v>
+        <v>1.2876</v>
       </c>
       <c r="G38">
         <v>0.019</v>
@@ -4525,28 +4525,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M38">
-        <v>0.08030447999999998</v>
+        <v>0.08253516</v>
       </c>
       <c r="N38">
-        <v>0.1863893975510204</v>
+        <v>0.1841587175510204</v>
       </c>
       <c r="O38">
-        <v>0.05591681926530613</v>
+        <v>0.05524761526530612</v>
       </c>
       <c r="P38">
-        <v>0.1304725782857143</v>
+        <v>0.1289111022857143</v>
       </c>
       <c r="Q38">
-        <v>0.1984725782857143</v>
+        <v>0.1969111022857143</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2425397347124902</v>
+        <v>0.2449904040537021</v>
       </c>
       <c r="T38">
-        <v>1.371756498538506</v>
+        <v>1.388843649741029</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.321033615447363</v>
+        <v>3.231275950165001</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1709458545538323</v>
+        <v>0.1705130788916709</v>
       </c>
       <c r="C39">
-        <v>2.735593687125895</v>
+        <v>2.714688922411312</v>
       </c>
       <c r="D39">
-        <v>4.004193687125895</v>
+        <v>4.018088922411312</v>
       </c>
       <c r="E39">
-        <v>-0.1624000000000001</v>
+        <v>-0.1276000000000002</v>
       </c>
       <c r="F39">
-        <v>1.2876</v>
+        <v>1.3224</v>
       </c>
       <c r="G39">
         <v>0.019</v>
@@ -4607,28 +4607,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M39">
-        <v>0.08253516</v>
+        <v>0.08476584</v>
       </c>
       <c r="N39">
-        <v>0.1841587175510204</v>
+        <v>0.1819280375510204</v>
       </c>
       <c r="O39">
-        <v>0.05524761526530612</v>
+        <v>0.05457841126530613</v>
       </c>
       <c r="P39">
-        <v>0.1289111022857143</v>
+        <v>0.1273496262857143</v>
       </c>
       <c r="Q39">
-        <v>0.1969111022857143</v>
+        <v>0.1953496262857143</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2449904040537021</v>
+        <v>0.2475201272446305</v>
       </c>
       <c r="T39">
-        <v>1.388843649741029</v>
+        <v>1.406481999369439</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.231275950165001</v>
+        <v>3.146242372529081</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1705130788916709</v>
+        <v>0.1700803032295095</v>
       </c>
       <c r="C40">
-        <v>2.714688922411312</v>
+        <v>2.693880931191728</v>
       </c>
       <c r="D40">
-        <v>4.018088922411312</v>
+        <v>4.032080931191728</v>
       </c>
       <c r="E40">
-        <v>-0.1276000000000002</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="F40">
-        <v>1.3224</v>
+        <v>1.3572</v>
       </c>
       <c r="G40">
         <v>0.019</v>
@@ -4689,28 +4689,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M40">
-        <v>0.08476584</v>
+        <v>0.08699652000000001</v>
       </c>
       <c r="N40">
-        <v>0.1819280375510204</v>
+        <v>0.1796973575510204</v>
       </c>
       <c r="O40">
-        <v>0.05457841126530613</v>
+        <v>0.05390920726530612</v>
       </c>
       <c r="P40">
-        <v>0.1273496262857143</v>
+        <v>0.1257881502857143</v>
       </c>
       <c r="Q40">
-        <v>0.1953496262857143</v>
+        <v>0.1937881502857143</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2475201272446305</v>
+        <v>0.2501327921795237</v>
       </c>
       <c r="T40">
-        <v>1.406481999369439</v>
+        <v>1.424698655543043</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.146242372529081</v>
+        <v>3.06556949118218</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1700803032295095</v>
+        <v>0.1718315275673481</v>
       </c>
       <c r="C41">
-        <v>2.693880931191728</v>
+        <v>2.603054646379265</v>
       </c>
       <c r="D41">
-        <v>4.032080931191728</v>
+        <v>3.976054646379265</v>
       </c>
       <c r="E41">
-        <v>-0.09279999999999999</v>
+        <v>-0.05800000000000005</v>
       </c>
       <c r="F41">
-        <v>1.3572</v>
+        <v>1.392</v>
       </c>
       <c r="G41">
         <v>0.019</v>
@@ -4771,45 +4771,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M41">
-        <v>0.08699652000000001</v>
+        <v>0.1000848</v>
       </c>
       <c r="N41">
-        <v>0.1796973575510204</v>
+        <v>0.1666090775510204</v>
       </c>
       <c r="O41">
-        <v>0.05390920726530612</v>
+        <v>0.04998272326530612</v>
       </c>
       <c r="P41">
-        <v>0.1257881502857143</v>
+        <v>0.1166263542857143</v>
       </c>
       <c r="Q41">
-        <v>0.1937881502857143</v>
+        <v>0.1846263542857143</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2501327921795237</v>
+        <v>0.2528325459455801</v>
       </c>
       <c r="T41">
-        <v>1.424698655543043</v>
+        <v>1.443522533589101</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.06556949118218</v>
+        <v>2.664679127609991</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1718315275673481</v>
+        <v>0.1714533519051867</v>
       </c>
       <c r="C42">
-        <v>2.603054646379265</v>
+        <v>2.580221275807656</v>
       </c>
       <c r="D42">
-        <v>3.976054646379265</v>
+        <v>3.988021275807656</v>
       </c>
       <c r="E42">
-        <v>-0.05800000000000005</v>
+        <v>-0.02320000000000011</v>
       </c>
       <c r="F42">
-        <v>1.392</v>
+        <v>1.4268</v>
       </c>
       <c r="G42">
         <v>0.019</v>
@@ -4853,28 +4853,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M42">
-        <v>0.1000848</v>
+        <v>0.10258692</v>
       </c>
       <c r="N42">
-        <v>0.1666090775510204</v>
+        <v>0.1641069575510204</v>
       </c>
       <c r="O42">
-        <v>0.04998272326530612</v>
+        <v>0.04923208726530613</v>
       </c>
       <c r="P42">
-        <v>0.1166263542857143</v>
+        <v>0.1148748702857143</v>
       </c>
       <c r="Q42">
-        <v>0.1846263542857143</v>
+        <v>0.1828748702857143</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2528325459455801</v>
+        <v>0.255623816788452</v>
       </c>
       <c r="T42">
-        <v>1.443522533589101</v>
+        <v>1.462984509196042</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.664679127609991</v>
+        <v>2.599686953765845</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1714533519051867</v>
+        <v>0.1710751762430252</v>
       </c>
       <c r="C43">
-        <v>2.580221275807656</v>
+        <v>2.557460153995036</v>
       </c>
       <c r="D43">
-        <v>3.988021275807656</v>
+        <v>4.000060153995036</v>
       </c>
       <c r="E43">
-        <v>-0.02320000000000011</v>
+        <v>0.01160000000000005</v>
       </c>
       <c r="F43">
-        <v>1.4268</v>
+        <v>1.4616</v>
       </c>
       <c r="G43">
         <v>0.019</v>
@@ -4935,28 +4935,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M43">
-        <v>0.10258692</v>
+        <v>0.10508904</v>
       </c>
       <c r="N43">
-        <v>0.1641069575510204</v>
+        <v>0.1616048375510204</v>
       </c>
       <c r="O43">
-        <v>0.04923208726530613</v>
+        <v>0.04848145126530612</v>
       </c>
       <c r="P43">
-        <v>0.1148748702857143</v>
+        <v>0.1131233862857143</v>
       </c>
       <c r="Q43">
-        <v>0.1828748702857143</v>
+        <v>0.1811233862857143</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.255623816788452</v>
+        <v>0.2585113383500435</v>
       </c>
       <c r="T43">
-        <v>1.462984509196042</v>
+        <v>1.483117587410118</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.599686953765845</v>
+        <v>2.537789645342848</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1710751762430252</v>
+        <v>0.1718709005808639</v>
       </c>
       <c r="C44">
-        <v>2.557460153995036</v>
+        <v>2.497412890727406</v>
       </c>
       <c r="D44">
-        <v>4.000060153995036</v>
+        <v>3.974812890727406</v>
       </c>
       <c r="E44">
-        <v>0.01159999999999983</v>
+        <v>0.04639999999999977</v>
       </c>
       <c r="F44">
-        <v>1.4616</v>
+        <v>1.4964</v>
       </c>
       <c r="G44">
         <v>0.019</v>
@@ -5017,45 +5017,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M44">
-        <v>0.10508904</v>
+        <v>0.11342712</v>
       </c>
       <c r="N44">
-        <v>0.1616048375510204</v>
+        <v>0.1532667575510204</v>
       </c>
       <c r="O44">
-        <v>0.04848145126530613</v>
+        <v>0.04598002726530612</v>
       </c>
       <c r="P44">
-        <v>0.1131233862857143</v>
+        <v>0.1072867302857143</v>
       </c>
       <c r="Q44">
-        <v>0.1811233862857143</v>
+        <v>0.1752867302857143</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2585113383500435</v>
+        <v>0.2615001764576558</v>
       </c>
       <c r="T44">
-        <v>1.483117587410118</v>
+        <v>1.50395708942118</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.537789645342849</v>
+        <v>2.351235555932483</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1718709005808639</v>
+        <v>0.1715200249187024</v>
       </c>
       <c r="C45">
-        <v>2.497412890727406</v>
+        <v>2.473706311253719</v>
       </c>
       <c r="D45">
-        <v>3.974812890727406</v>
+        <v>3.985906311253719</v>
       </c>
       <c r="E45">
-        <v>0.04639999999999977</v>
+        <v>0.08119999999999994</v>
       </c>
       <c r="F45">
-        <v>1.4964</v>
+        <v>1.5312</v>
       </c>
       <c r="G45">
         <v>0.019</v>
@@ -5099,28 +5099,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M45">
-        <v>0.11342712</v>
+        <v>0.11606496</v>
       </c>
       <c r="N45">
-        <v>0.1532667575510204</v>
+        <v>0.1506289175510204</v>
       </c>
       <c r="O45">
-        <v>0.04598002726530612</v>
+        <v>0.04518867526530613</v>
       </c>
       <c r="P45">
-        <v>0.1072867302857143</v>
+        <v>0.1054402422857143</v>
       </c>
       <c r="Q45">
-        <v>0.1752867302857143</v>
+        <v>0.1734402422857143</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2615001764576558</v>
+        <v>0.2645957587833971</v>
       </c>
       <c r="T45">
-        <v>1.50395708942118</v>
+        <v>1.525540859361209</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.351235555932483</v>
+        <v>2.297798384206744</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1715200249187024</v>
+        <v>0.171169149256541</v>
       </c>
       <c r="C46">
-        <v>2.473706311253719</v>
+        <v>2.450061826981218</v>
       </c>
       <c r="D46">
-        <v>3.985906311253719</v>
+        <v>3.997061826981217</v>
       </c>
       <c r="E46">
-        <v>0.08119999999999994</v>
+        <v>0.1159999999999999</v>
       </c>
       <c r="F46">
-        <v>1.5312</v>
+        <v>1.566</v>
       </c>
       <c r="G46">
         <v>0.019</v>
@@ -5181,28 +5181,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M46">
-        <v>0.11606496</v>
+        <v>0.1187028</v>
       </c>
       <c r="N46">
-        <v>0.1506289175510204</v>
+        <v>0.1479910775510204</v>
       </c>
       <c r="O46">
-        <v>0.04518867526530613</v>
+        <v>0.04439732326530613</v>
       </c>
       <c r="P46">
-        <v>0.1054402422857143</v>
+        <v>0.1035937542857143</v>
       </c>
       <c r="Q46">
-        <v>0.1734402422857143</v>
+        <v>0.1715937542857143</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2645957587833971</v>
+        <v>0.2678039077391655</v>
       </c>
       <c r="T46">
-        <v>1.525540859361209</v>
+        <v>1.547909493662693</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.297798384206744</v>
+        <v>2.246736197891039</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.171169149256541</v>
+        <v>0.1708182735943796</v>
       </c>
       <c r="C47">
-        <v>2.450061826981218</v>
+        <v>2.426479960738148</v>
       </c>
       <c r="D47">
-        <v>3.997061826981217</v>
+        <v>4.008279960738148</v>
       </c>
       <c r="E47">
-        <v>0.1159999999999999</v>
+        <v>0.1507999999999998</v>
       </c>
       <c r="F47">
-        <v>1.566</v>
+        <v>1.6008</v>
       </c>
       <c r="G47">
         <v>0.019</v>
@@ -5263,28 +5263,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M47">
-        <v>0.1187028</v>
+        <v>0.12134064</v>
       </c>
       <c r="N47">
-        <v>0.1479910775510204</v>
+        <v>0.1453532375510204</v>
       </c>
       <c r="O47">
-        <v>0.04439732326530613</v>
+        <v>0.04360597126530612</v>
       </c>
       <c r="P47">
-        <v>0.1035937542857143</v>
+        <v>0.1017472662857143</v>
       </c>
       <c r="Q47">
-        <v>0.1715937542857143</v>
+        <v>0.1697472662857143</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2678039077391655</v>
+        <v>0.2711308770266289</v>
       </c>
       <c r="T47">
-        <v>1.547909493662693</v>
+        <v>1.571106595901268</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.246736197891039</v>
+        <v>2.197894106632538</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1708182735943796</v>
+        <v>0.1704673979322182</v>
       </c>
       <c r="C48">
-        <v>2.426479960738148</v>
+        <v>2.40296124123874</v>
       </c>
       <c r="D48">
-        <v>4.008279960738148</v>
+        <v>4.01956124123874</v>
       </c>
       <c r="E48">
-        <v>0.1507999999999998</v>
+        <v>0.1856</v>
       </c>
       <c r="F48">
-        <v>1.6008</v>
+        <v>1.6356</v>
       </c>
       <c r="G48">
         <v>0.019</v>
@@ -5345,28 +5345,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M48">
-        <v>0.12134064</v>
+        <v>0.12397848</v>
       </c>
       <c r="N48">
-        <v>0.1453532375510204</v>
+        <v>0.1427153975510204</v>
       </c>
       <c r="O48">
-        <v>0.04360597126530612</v>
+        <v>0.04281461926530612</v>
       </c>
       <c r="P48">
-        <v>0.1017472662857143</v>
+        <v>0.0999007782857143</v>
       </c>
       <c r="Q48">
-        <v>0.1697472662857143</v>
+        <v>0.1679007782857143</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2711308770266289</v>
+        <v>0.2745833923249399</v>
       </c>
       <c r="T48">
-        <v>1.571106595901268</v>
+        <v>1.59517906048847</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.197894106632538</v>
+        <v>2.151130402236101</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1704673979322182</v>
+        <v>0.1701165222700568</v>
       </c>
       <c r="C49">
-        <v>2.40296124123874</v>
+        <v>2.379506203166279</v>
       </c>
       <c r="D49">
-        <v>4.01956124123874</v>
+        <v>4.030906203166279</v>
       </c>
       <c r="E49">
-        <v>0.1856</v>
+        <v>0.2203999999999999</v>
       </c>
       <c r="F49">
-        <v>1.6356</v>
+        <v>1.6704</v>
       </c>
       <c r="G49">
         <v>0.019</v>
@@ -5427,28 +5427,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M49">
-        <v>0.12397848</v>
+        <v>0.12661632</v>
       </c>
       <c r="N49">
-        <v>0.1427153975510204</v>
+        <v>0.1400775575510204</v>
       </c>
       <c r="O49">
-        <v>0.04281461926530612</v>
+        <v>0.04202326726530612</v>
       </c>
       <c r="P49">
-        <v>0.0999007782857143</v>
+        <v>0.0980542902857143</v>
       </c>
       <c r="Q49">
-        <v>0.1679007782857143</v>
+        <v>0.1660542902857143</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2745833923249399</v>
+        <v>0.2781686966731861</v>
       </c>
       <c r="T49">
-        <v>1.59517906048847</v>
+        <v>1.620177389098256</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.151130402236101</v>
+        <v>2.106315185522849</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1701165222700567</v>
+        <v>0.1697656466078953</v>
       </c>
       <c r="C50">
-        <v>2.37950620316628</v>
+        <v>2.356115387257582</v>
       </c>
       <c r="D50">
-        <v>4.03090620316628</v>
+        <v>4.042315387257581</v>
       </c>
       <c r="E50">
-        <v>0.2203999999999997</v>
+        <v>0.2551999999999999</v>
       </c>
       <c r="F50">
-        <v>1.6704</v>
+        <v>1.7052</v>
       </c>
       <c r="G50">
         <v>0.019</v>
@@ -5509,28 +5509,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M50">
-        <v>0.12661632</v>
+        <v>0.12925416</v>
       </c>
       <c r="N50">
-        <v>0.1400775575510204</v>
+        <v>0.1374397175510204</v>
       </c>
       <c r="O50">
-        <v>0.04202326726530613</v>
+        <v>0.04123191526530613</v>
       </c>
       <c r="P50">
-        <v>0.0980542902857143</v>
+        <v>0.09620780228571429</v>
       </c>
       <c r="Q50">
-        <v>0.1660542902857143</v>
+        <v>0.1642078022857143</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2781686966731861</v>
+        <v>0.2818946011919516</v>
       </c>
       <c r="T50">
-        <v>1.620177389098256</v>
+        <v>1.646156044320191</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.106315185522849</v>
+        <v>2.063329161328505</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1697656466078953</v>
+        <v>0.1694147709457339</v>
       </c>
       <c r="C51">
-        <v>2.356115387257582</v>
+        <v>2.332789340388893</v>
       </c>
       <c r="D51">
-        <v>4.042315387257581</v>
+        <v>4.053789340388892</v>
       </c>
       <c r="E51">
-        <v>0.2551999999999999</v>
+        <v>0.2899999999999998</v>
       </c>
       <c r="F51">
-        <v>1.7052</v>
+        <v>1.74</v>
       </c>
       <c r="G51">
         <v>0.019</v>
@@ -5591,28 +5591,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M51">
-        <v>0.12925416</v>
+        <v>0.131892</v>
       </c>
       <c r="N51">
-        <v>0.1374397175510204</v>
+        <v>0.1348018775510204</v>
       </c>
       <c r="O51">
-        <v>0.04123191526530613</v>
+        <v>0.04044056326530613</v>
       </c>
       <c r="P51">
-        <v>0.09620780228571429</v>
+        <v>0.09436131428571432</v>
       </c>
       <c r="Q51">
-        <v>0.1642078022857143</v>
+        <v>0.1623613142857143</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2818946011919516</v>
+        <v>0.2857695418914679</v>
       </c>
       <c r="T51">
-        <v>1.646156044320191</v>
+        <v>1.673173845751003</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.063329161328505</v>
+        <v>2.022062578101935</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1694147709457339</v>
+        <v>0.1741332952835725</v>
       </c>
       <c r="C52">
-        <v>2.332789340388893</v>
+        <v>2.148940696225043</v>
       </c>
       <c r="D52">
-        <v>4.053789340388892</v>
+        <v>3.904740696225042</v>
       </c>
       <c r="E52">
-        <v>0.2899999999999998</v>
+        <v>0.3247999999999998</v>
       </c>
       <c r="F52">
-        <v>1.74</v>
+        <v>1.7748</v>
       </c>
       <c r="G52">
         <v>0.019</v>
@@ -5673,45 +5673,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M52">
-        <v>0.131892</v>
+        <v>0.159732</v>
       </c>
       <c r="N52">
-        <v>0.1348018775510204</v>
+        <v>0.1069618775510205</v>
       </c>
       <c r="O52">
-        <v>0.04044056326530613</v>
+        <v>0.03208856326530614</v>
       </c>
       <c r="P52">
-        <v>0.09436131428571432</v>
+        <v>0.07487331428571432</v>
       </c>
       <c r="Q52">
-        <v>0.1623613142857143</v>
+        <v>0.1428733142857143</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2857695418914679</v>
+        <v>0.2898026434358623</v>
       </c>
       <c r="T52">
-        <v>1.673173845751003</v>
+        <v>1.701294414587154</v>
       </c>
       <c r="U52">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.022062578101935</v>
+        <v>1.669633370589616</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1741332952835725</v>
+        <v>0.1738818196214111</v>
       </c>
       <c r="C53">
-        <v>2.148940696225043</v>
+        <v>2.12180725854477</v>
       </c>
       <c r="D53">
-        <v>3.904740696225042</v>
+        <v>3.91240725854477</v>
       </c>
       <c r="E53">
-        <v>0.3247999999999998</v>
+        <v>0.3595999999999999</v>
       </c>
       <c r="F53">
-        <v>1.7748</v>
+        <v>1.8096</v>
       </c>
       <c r="G53">
         <v>0.019</v>
@@ -5755,28 +5755,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M53">
-        <v>0.159732</v>
+        <v>0.162864</v>
       </c>
       <c r="N53">
-        <v>0.1069618775510205</v>
+        <v>0.1038298775510204</v>
       </c>
       <c r="O53">
-        <v>0.03208856326530614</v>
+        <v>0.03114896326530613</v>
       </c>
       <c r="P53">
-        <v>0.07487331428571432</v>
+        <v>0.07268091428571431</v>
       </c>
       <c r="Q53">
-        <v>0.1428733142857143</v>
+        <v>0.1406809142857143</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2898026434358623</v>
+        <v>0.2940037908779398</v>
       </c>
       <c r="T53">
-        <v>1.701294414587154</v>
+        <v>1.730586673791479</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.669633370589616</v>
+        <v>1.637525036539815</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1738818196214111</v>
+        <v>0.1736303439592497</v>
       </c>
       <c r="C54">
-        <v>2.12180725854477</v>
+        <v>2.094703985124035</v>
       </c>
       <c r="D54">
-        <v>3.91240725854477</v>
+        <v>3.920103985124034</v>
       </c>
       <c r="E54">
-        <v>0.3595999999999999</v>
+        <v>0.3943999999999999</v>
       </c>
       <c r="F54">
-        <v>1.8096</v>
+        <v>1.8444</v>
       </c>
       <c r="G54">
         <v>0.019</v>
@@ -5837,28 +5837,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M54">
-        <v>0.162864</v>
+        <v>0.165996</v>
       </c>
       <c r="N54">
-        <v>0.1038298775510204</v>
+        <v>0.1006978775510204</v>
       </c>
       <c r="O54">
-        <v>0.03114896326530613</v>
+        <v>0.03020936326530613</v>
       </c>
       <c r="P54">
-        <v>0.07268091428571431</v>
+        <v>0.07048851428571432</v>
       </c>
       <c r="Q54">
-        <v>0.1406809142857143</v>
+        <v>0.1384885142857143</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2940037908779398</v>
+        <v>0.2983837105515951</v>
       </c>
       <c r="T54">
-        <v>1.730586673791479</v>
+        <v>1.761125412110881</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.637525036539815</v>
+        <v>1.606628337737177</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1736303439592497</v>
+        <v>0.1733788682970882</v>
       </c>
       <c r="C55">
-        <v>2.094703985124035</v>
+        <v>2.067631054336666</v>
       </c>
       <c r="D55">
-        <v>3.920103985124034</v>
+        <v>3.927831054336666</v>
       </c>
       <c r="E55">
-        <v>0.3943999999999999</v>
+        <v>0.4292</v>
       </c>
       <c r="F55">
-        <v>1.8444</v>
+        <v>1.8792</v>
       </c>
       <c r="G55">
         <v>0.019</v>
@@ -5919,28 +5919,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M55">
-        <v>0.165996</v>
+        <v>0.169128</v>
       </c>
       <c r="N55">
-        <v>0.1006978775510204</v>
+        <v>0.09756587755102042</v>
       </c>
       <c r="O55">
-        <v>0.03020936326530613</v>
+        <v>0.02926976326530613</v>
       </c>
       <c r="P55">
-        <v>0.07048851428571432</v>
+        <v>0.06829611428571429</v>
       </c>
       <c r="Q55">
-        <v>0.1384885142857143</v>
+        <v>0.1362961142857143</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2983837105515951</v>
+        <v>0.3029540615154093</v>
       </c>
       <c r="T55">
-        <v>1.761125412110881</v>
+        <v>1.792991921661561</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.606628337737177</v>
+        <v>1.576875961112414</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1733788682970882</v>
+        <v>0.1731273926349268</v>
       </c>
       <c r="C56">
-        <v>2.067631054336666</v>
+        <v>2.040588645965669</v>
       </c>
       <c r="D56">
-        <v>3.927831054336666</v>
+        <v>3.935588645965669</v>
       </c>
       <c r="E56">
-        <v>0.4292</v>
+        <v>0.464</v>
       </c>
       <c r="F56">
-        <v>1.8792</v>
+        <v>1.914</v>
       </c>
       <c r="G56">
         <v>0.019</v>
@@ -6001,28 +6001,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M56">
-        <v>0.169128</v>
+        <v>0.17226</v>
       </c>
       <c r="N56">
-        <v>0.09756587755102042</v>
+        <v>0.09443387755102042</v>
       </c>
       <c r="O56">
-        <v>0.02926976326530613</v>
+        <v>0.02833016326530613</v>
       </c>
       <c r="P56">
-        <v>0.06829611428571429</v>
+        <v>0.06610371428571429</v>
       </c>
       <c r="Q56">
-        <v>0.1362961142857143</v>
+        <v>0.1341037142857143</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3029540615154093</v>
+        <v>0.3077275391887264</v>
       </c>
       <c r="T56">
-        <v>1.792991921661561</v>
+        <v>1.826274720525605</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.576875961112414</v>
+        <v>1.548205489092189</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1731273926349268</v>
+        <v>0.1728759169727655</v>
       </c>
       <c r="C57">
-        <v>2.040588645965669</v>
+        <v>2.013576941217169</v>
       </c>
       <c r="D57">
-        <v>3.935588645965669</v>
+        <v>3.943376941217168</v>
       </c>
       <c r="E57">
-        <v>0.464</v>
+        <v>0.4987999999999999</v>
       </c>
       <c r="F57">
-        <v>1.914</v>
+        <v>1.9488</v>
       </c>
       <c r="G57">
         <v>0.019</v>
@@ -6083,28 +6083,28 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M57">
-        <v>0.17226</v>
+        <v>0.175392</v>
       </c>
       <c r="N57">
-        <v>0.09443387755102042</v>
+        <v>0.09130187755102043</v>
       </c>
       <c r="O57">
-        <v>0.02833016326530613</v>
+        <v>0.02739056326530613</v>
       </c>
       <c r="P57">
-        <v>0.06610371428571429</v>
+        <v>0.0639113142857143</v>
       </c>
       <c r="Q57">
-        <v>0.1341037142857143</v>
+        <v>0.1319113142857143</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3077275391887264</v>
+        <v>0.3127179931199215</v>
       </c>
       <c r="T57">
-        <v>1.826274720525605</v>
+        <v>1.861070373883469</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.548205489092189</v>
+        <v>1.520558962501257</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1728759169727655</v>
+        <v>0.1994303772271379</v>
       </c>
       <c r="C58">
-        <v>2.013576941217169</v>
+        <v>1.297178365834234</v>
       </c>
       <c r="D58">
-        <v>3.943376941217168</v>
+        <v>3.261778365834234</v>
       </c>
       <c r="E58">
-        <v>0.4987999999999999</v>
+        <v>0.5336000000000001</v>
       </c>
       <c r="F58">
-        <v>1.9488</v>
+        <v>1.9836</v>
       </c>
       <c r="G58">
         <v>0.019</v>
@@ -6165,45 +6165,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M58">
-        <v>0.175392</v>
+        <v>0.29119248</v>
       </c>
       <c r="N58">
-        <v>0.09130187755102043</v>
+        <v>-0.02449860244897961</v>
       </c>
       <c r="O58">
-        <v>0.02739056326530613</v>
+        <v>-0.007349580734693884</v>
       </c>
       <c r="P58">
-        <v>0.0639113142857143</v>
+        <v>-0.01714902171428573</v>
       </c>
       <c r="Q58">
-        <v>0.1319113142857143</v>
+        <v>0.05085097828571428</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3127179931199215</v>
+        <v>0.3226633226515277</v>
       </c>
       <c r="T58">
-        <v>1.861070373883469</v>
+        <v>1.930413612731608</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.3</v>
+        <v>0.2747604033775395</v>
       </c>
       <c r="W58">
-        <v>0.063</v>
+        <v>0.1064651727841772</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.520558962501257</v>
+        <v>0.9158680112584652</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1994303772271379</v>
+        <v>0.2004403772271379</v>
       </c>
       <c r="C59">
-        <v>1.297178365834234</v>
+        <v>1.241074769654733</v>
       </c>
       <c r="D59">
-        <v>3.261778365834234</v>
+        <v>3.240474769654733</v>
       </c>
       <c r="E59">
-        <v>0.5336000000000001</v>
+        <v>0.5684000000000002</v>
       </c>
       <c r="F59">
-        <v>1.9836</v>
+        <v>2.0184</v>
       </c>
       <c r="G59">
         <v>0.019</v>
@@ -6247,37 +6247,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M59">
-        <v>0.29119248</v>
+        <v>0.29630112</v>
       </c>
       <c r="N59">
-        <v>-0.02449860244897961</v>
+        <v>-0.02960724244897961</v>
       </c>
       <c r="O59">
-        <v>-0.007349580734693884</v>
+        <v>-0.008882172734693883</v>
       </c>
       <c r="P59">
-        <v>-0.01714902171428573</v>
+        <v>-0.02072506971428573</v>
       </c>
       <c r="Q59">
-        <v>0.05085097828571428</v>
+        <v>0.04727493028571428</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3226633226515277</v>
+        <v>0.3292553065241831</v>
       </c>
       <c r="T59">
-        <v>1.930413612731608</v>
+        <v>1.97637584160617</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2747604033775395</v>
+        <v>0.270023155043444</v>
       </c>
       <c r="W59">
-        <v>0.1064651727841772</v>
+        <v>0.1071606008396224</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9158680112584652</v>
+        <v>0.9000771834781468</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2004403772271379</v>
+        <v>0.2014503772271379</v>
       </c>
       <c r="C60">
-        <v>1.241074769654734</v>
+        <v>1.185247647358878</v>
       </c>
       <c r="D60">
-        <v>3.240474769654734</v>
+        <v>3.219447647358877</v>
       </c>
       <c r="E60">
-        <v>0.5683999999999998</v>
+        <v>0.6031999999999995</v>
       </c>
       <c r="F60">
-        <v>2.0184</v>
+        <v>2.053199999999999</v>
       </c>
       <c r="G60">
         <v>0.019</v>
@@ -6329,37 +6329,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M60">
-        <v>0.29630112</v>
+        <v>0.30140976</v>
       </c>
       <c r="N60">
-        <v>-0.02960724244897955</v>
+        <v>-0.03471588244897955</v>
       </c>
       <c r="O60">
-        <v>-0.008882172734693865</v>
+        <v>-0.01041476473469386</v>
       </c>
       <c r="P60">
-        <v>-0.02072506971428569</v>
+        <v>-0.02430111771428569</v>
       </c>
       <c r="Q60">
-        <v>0.04727493028571432</v>
+        <v>0.04369888228571432</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3292553065241831</v>
+        <v>0.3361688505857485</v>
       </c>
       <c r="T60">
-        <v>1.976375841606169</v>
+        <v>2.024580130425832</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2700231550434441</v>
+        <v>0.26544649139864</v>
       </c>
       <c r="W60">
-        <v>0.1071606008396224</v>
+        <v>0.1078324550626797</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9000771834781469</v>
+        <v>0.8848216379954665</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2014503772271379</v>
+        <v>0.2024603772271379</v>
       </c>
       <c r="C61">
-        <v>1.185247647358878</v>
+        <v>1.129691651609436</v>
       </c>
       <c r="D61">
-        <v>3.219447647358877</v>
+        <v>3.198691651609435</v>
       </c>
       <c r="E61">
-        <v>0.6031999999999995</v>
+        <v>0.6379999999999997</v>
       </c>
       <c r="F61">
-        <v>2.053199999999999</v>
+        <v>2.088</v>
       </c>
       <c r="G61">
         <v>0.019</v>
@@ -6411,37 +6411,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M61">
-        <v>0.30140976</v>
+        <v>0.3065184</v>
       </c>
       <c r="N61">
-        <v>-0.03471588244897955</v>
+        <v>-0.03982452244897955</v>
       </c>
       <c r="O61">
-        <v>-0.01041476473469386</v>
+        <v>-0.01194735673469386</v>
       </c>
       <c r="P61">
-        <v>-0.02430111771428569</v>
+        <v>-0.02787716571428569</v>
       </c>
       <c r="Q61">
-        <v>0.04369888228571432</v>
+        <v>0.04012283428571432</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3361688505857485</v>
+        <v>0.3434280718503921</v>
       </c>
       <c r="T61">
-        <v>2.024580130425832</v>
+        <v>2.075194633686477</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.26544649139864</v>
+        <v>0.2610223832086626</v>
       </c>
       <c r="W61">
-        <v>0.1078324550626797</v>
+        <v>0.1084819141449683</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8848216379954665</v>
+        <v>0.8700746106955421</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2024603772271379</v>
+        <v>0.2034703772271379</v>
       </c>
       <c r="C62">
-        <v>1.129691651609436</v>
+        <v>1.074401572084405</v>
       </c>
       <c r="D62">
-        <v>3.198691651609435</v>
+        <v>3.178201572084405</v>
       </c>
       <c r="E62">
-        <v>0.6379999999999997</v>
+        <v>0.6727999999999998</v>
       </c>
       <c r="F62">
-        <v>2.088</v>
+        <v>2.1228</v>
       </c>
       <c r="G62">
         <v>0.019</v>
@@ -6493,37 +6493,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M62">
-        <v>0.3065184</v>
+        <v>0.31162704</v>
       </c>
       <c r="N62">
-        <v>-0.03982452244897955</v>
+        <v>-0.0449331624489796</v>
       </c>
       <c r="O62">
-        <v>-0.01194735673469386</v>
+        <v>-0.01347994873469388</v>
       </c>
       <c r="P62">
-        <v>-0.02787716571428569</v>
+        <v>-0.03145321371428572</v>
       </c>
       <c r="Q62">
-        <v>0.04012283428571432</v>
+        <v>0.03654678628571428</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3434280718503921</v>
+        <v>0.3510595608721972</v>
       </c>
       <c r="T62">
-        <v>2.075194633686477</v>
+        <v>2.128404752498952</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2610223832086626</v>
+        <v>0.2567433277462255</v>
       </c>
       <c r="W62">
-        <v>0.1084819141449683</v>
+        <v>0.1091100794868541</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8700746106955421</v>
+        <v>0.8558110924874183</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2034703772271379</v>
+        <v>0.2044803772271379</v>
       </c>
       <c r="C63">
-        <v>1.074401572084405</v>
+        <v>1.019372331116504</v>
       </c>
       <c r="D63">
-        <v>3.178201572084405</v>
+        <v>3.157972331116503</v>
       </c>
       <c r="E63">
-        <v>0.6727999999999998</v>
+        <v>0.7075999999999996</v>
       </c>
       <c r="F63">
-        <v>2.1228</v>
+        <v>2.1576</v>
       </c>
       <c r="G63">
         <v>0.019</v>
@@ -6575,37 +6575,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M63">
-        <v>0.31162704</v>
+        <v>0.31673568</v>
       </c>
       <c r="N63">
-        <v>-0.0449331624489796</v>
+        <v>-0.05004180244897954</v>
       </c>
       <c r="O63">
-        <v>-0.01347994873469388</v>
+        <v>-0.01501254073469386</v>
       </c>
       <c r="P63">
-        <v>-0.03145321371428572</v>
+        <v>-0.03502926171428568</v>
       </c>
       <c r="Q63">
-        <v>0.03654678628571428</v>
+        <v>0.03297073828571433</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3510595608721972</v>
+        <v>0.3590927072109392</v>
       </c>
       <c r="T63">
-        <v>2.128404752498952</v>
+        <v>2.184415403880503</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2567433277462255</v>
+        <v>0.2526023063309638</v>
       </c>
       <c r="W63">
-        <v>0.1091100794868541</v>
+        <v>0.1097179814306145</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8558110924874183</v>
+        <v>0.8420076877698794</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2044803772271379</v>
+        <v>0.2054903772271379</v>
       </c>
       <c r="C64">
-        <v>1.019372331116504</v>
+        <v>0.9645989794981342</v>
       </c>
       <c r="D64">
-        <v>3.157972331116503</v>
+        <v>3.137998979498134</v>
       </c>
       <c r="E64">
-        <v>0.7075999999999996</v>
+        <v>0.7423999999999997</v>
       </c>
       <c r="F64">
-        <v>2.1576</v>
+        <v>2.1924</v>
       </c>
       <c r="G64">
         <v>0.019</v>
@@ -6657,37 +6657,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M64">
-        <v>0.31673568</v>
+        <v>0.32184432</v>
       </c>
       <c r="N64">
-        <v>-0.05004180244897954</v>
+        <v>-0.05515044244897954</v>
       </c>
       <c r="O64">
-        <v>-0.01501254073469386</v>
+        <v>-0.01654513273469386</v>
       </c>
       <c r="P64">
-        <v>-0.03502926171428568</v>
+        <v>-0.03860530971428568</v>
       </c>
       <c r="Q64">
-        <v>0.03297073828571433</v>
+        <v>0.02939469028571433</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3590927072109392</v>
+        <v>0.3675600776760997</v>
       </c>
       <c r="T64">
-        <v>2.184415403880503</v>
+        <v>2.243453658039436</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2526023063309638</v>
+        <v>0.248592745913012</v>
       </c>
       <c r="W64">
-        <v>0.1097179814306145</v>
+        <v>0.1103065848999698</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8420076877698794</v>
+        <v>0.8286424863767068</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2054903772271379</v>
+        <v>0.2065003772271379</v>
       </c>
       <c r="C65">
-        <v>0.9645989794981342</v>
+        <v>0.9100766924445489</v>
       </c>
       <c r="D65">
-        <v>3.137998979498134</v>
+        <v>3.118276692444549</v>
       </c>
       <c r="E65">
-        <v>0.7423999999999997</v>
+        <v>0.7771999999999999</v>
       </c>
       <c r="F65">
-        <v>2.1924</v>
+        <v>2.2272</v>
       </c>
       <c r="G65">
         <v>0.019</v>
@@ -6739,37 +6739,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M65">
-        <v>0.32184432</v>
+        <v>0.32695296</v>
       </c>
       <c r="N65">
-        <v>-0.05515044244897954</v>
+        <v>-0.0602590824489796</v>
       </c>
       <c r="O65">
-        <v>-0.01654513273469386</v>
+        <v>-0.01807772473469388</v>
       </c>
       <c r="P65">
-        <v>-0.03860530971428568</v>
+        <v>-0.04218135771428572</v>
       </c>
       <c r="Q65">
-        <v>0.02939469028571433</v>
+        <v>0.02581864228571429</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3675600776760997</v>
+        <v>0.376497857611547</v>
       </c>
       <c r="T65">
-        <v>2.243453658039436</v>
+        <v>2.305771815207198</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.248592745913012</v>
+        <v>0.2447084842581212</v>
       </c>
       <c r="W65">
-        <v>0.1103065848999698</v>
+        <v>0.1108767945109078</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8286424863767068</v>
+        <v>0.8156949475270706</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2065003772271379</v>
+        <v>0.2075103772271379</v>
       </c>
       <c r="C66">
-        <v>0.9100766924445489</v>
+        <v>0.8558007657082869</v>
       </c>
       <c r="D66">
-        <v>3.118276692444549</v>
+        <v>3.098800765708286</v>
       </c>
       <c r="E66">
-        <v>0.7771999999999999</v>
+        <v>0.8119999999999996</v>
       </c>
       <c r="F66">
-        <v>2.2272</v>
+        <v>2.262</v>
       </c>
       <c r="G66">
         <v>0.019</v>
@@ -6821,37 +6821,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M66">
-        <v>0.32695296</v>
+        <v>0.3320616</v>
       </c>
       <c r="N66">
-        <v>-0.0602590824489796</v>
+        <v>-0.06536772244897954</v>
       </c>
       <c r="O66">
-        <v>-0.01807772473469388</v>
+        <v>-0.01961031673469386</v>
       </c>
       <c r="P66">
-        <v>-0.04218135771428572</v>
+        <v>-0.04575740571428567</v>
       </c>
       <c r="Q66">
-        <v>0.02581864228571429</v>
+        <v>0.02224259428571433</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.376497857611547</v>
+        <v>0.3859463678290198</v>
       </c>
       <c r="T66">
-        <v>2.305771815207198</v>
+        <v>2.371651009927404</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2447084842581212</v>
+        <v>0.2409437383464578</v>
       </c>
       <c r="W66">
-        <v>0.1108767945109078</v>
+        <v>0.11142945921074</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8156949475270706</v>
+        <v>0.8031457944881927</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2075103772271379</v>
+        <v>0.2501055742736368</v>
       </c>
       <c r="C67">
-        <v>0.8558007657082869</v>
+        <v>0.1749389551460365</v>
       </c>
       <c r="D67">
-        <v>3.098800765708286</v>
+        <v>2.452738955146036</v>
       </c>
       <c r="E67">
-        <v>0.8119999999999996</v>
+        <v>0.8467999999999998</v>
       </c>
       <c r="F67">
-        <v>2.262</v>
+        <v>2.2968</v>
       </c>
       <c r="G67">
         <v>0.019</v>
@@ -6903,45 +6903,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M67">
-        <v>0.3320616</v>
+        <v>0.46119744</v>
       </c>
       <c r="N67">
-        <v>-0.06536772244897954</v>
+        <v>-0.1945035624489795</v>
       </c>
       <c r="O67">
-        <v>-0.01961031673469386</v>
+        <v>-0.05835106873469386</v>
       </c>
       <c r="P67">
-        <v>-0.04575740571428567</v>
+        <v>-0.1361524937142857</v>
       </c>
       <c r="Q67">
-        <v>0.02224259428571433</v>
+        <v>-0.06815249371428567</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3859463678290198</v>
+        <v>0.4134365464313406</v>
       </c>
       <c r="T67">
-        <v>2.371651009927404</v>
+        <v>2.563324701054546</v>
       </c>
       <c r="U67">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.2409437383464578</v>
+        <v>0.1734792007199913</v>
       </c>
       <c r="W67">
-        <v>0.11142945921074</v>
+        <v>0.1659653764954258</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8031457944881927</v>
+        <v>0.578264002399971</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2501055742736368</v>
+        <v>0.2516555742736368</v>
       </c>
       <c r="C68">
-        <v>0.1749389551460365</v>
+        <v>0.1216709326312673</v>
       </c>
       <c r="D68">
-        <v>2.452738955146036</v>
+        <v>2.434270932631267</v>
       </c>
       <c r="E68">
-        <v>0.8467999999999998</v>
+        <v>0.8815999999999999</v>
       </c>
       <c r="F68">
-        <v>2.2968</v>
+        <v>2.3316</v>
       </c>
       <c r="G68">
         <v>0.019</v>
@@ -6985,37 +6985,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M68">
-        <v>0.46119744</v>
+        <v>0.46818528</v>
       </c>
       <c r="N68">
-        <v>-0.1945035624489795</v>
+        <v>-0.2014914024489796</v>
       </c>
       <c r="O68">
-        <v>-0.05835106873469386</v>
+        <v>-0.06044742073469386</v>
       </c>
       <c r="P68">
-        <v>-0.1361524937142857</v>
+        <v>-0.1410439817142857</v>
       </c>
       <c r="Q68">
-        <v>-0.06815249371428567</v>
+        <v>-0.07304398171428569</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4134365464313406</v>
+        <v>0.4245770478383509</v>
       </c>
       <c r="T68">
-        <v>2.563324701054546</v>
+        <v>2.641001207147108</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1734792007199913</v>
+        <v>0.1708899589182004</v>
       </c>
       <c r="W68">
-        <v>0.1659653764954258</v>
+        <v>0.1664852962492254</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.578264002399971</v>
+        <v>0.5696331963940011</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2516555742736368</v>
+        <v>0.2532055742736368</v>
       </c>
       <c r="C69">
-        <v>0.1216709326312673</v>
+        <v>0.06867894353554238</v>
       </c>
       <c r="D69">
-        <v>2.434270932631267</v>
+        <v>2.416078943535542</v>
       </c>
       <c r="E69">
-        <v>0.8815999999999999</v>
+        <v>0.9164000000000001</v>
       </c>
       <c r="F69">
-        <v>2.3316</v>
+        <v>2.3664</v>
       </c>
       <c r="G69">
         <v>0.019</v>
@@ -7067,37 +7067,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M69">
-        <v>0.46818528</v>
+        <v>0.47517312</v>
       </c>
       <c r="N69">
-        <v>-0.2014914024489796</v>
+        <v>-0.2084792424489796</v>
       </c>
       <c r="O69">
-        <v>-0.06044742073469386</v>
+        <v>-0.06254377273469387</v>
       </c>
       <c r="P69">
-        <v>-0.1410439817142857</v>
+        <v>-0.1459354697142857</v>
       </c>
       <c r="Q69">
-        <v>-0.07304398171428569</v>
+        <v>-0.07793546971428572</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4245770478383509</v>
+        <v>0.4364138305832994</v>
       </c>
       <c r="T69">
-        <v>2.641001207147108</v>
+        <v>2.723532494870455</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1708899589182004</v>
+        <v>0.1683768712870503</v>
       </c>
       <c r="W69">
-        <v>0.1664852962492254</v>
+        <v>0.1669899242455603</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5696331963940011</v>
+        <v>0.5612562376235011</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2532055742736368</v>
+        <v>0.2547555742736368</v>
       </c>
       <c r="C70">
-        <v>0.06867894353554238</v>
+        <v>0.01595684513975604</v>
       </c>
       <c r="D70">
-        <v>2.416078943535542</v>
+        <v>2.398156845139756</v>
       </c>
       <c r="E70">
-        <v>0.9164000000000001</v>
+        <v>0.9511999999999998</v>
       </c>
       <c r="F70">
-        <v>2.3664</v>
+        <v>2.4012</v>
       </c>
       <c r="G70">
         <v>0.019</v>
@@ -7149,37 +7149,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M70">
-        <v>0.47517312</v>
+        <v>0.48216096</v>
       </c>
       <c r="N70">
-        <v>-0.2084792424489796</v>
+        <v>-0.2154670824489796</v>
       </c>
       <c r="O70">
-        <v>-0.06254377273469387</v>
+        <v>-0.06464012473469387</v>
       </c>
       <c r="P70">
-        <v>-0.1459354697142857</v>
+        <v>-0.1508269577142857</v>
       </c>
       <c r="Q70">
-        <v>-0.07793546971428572</v>
+        <v>-0.08282695771428567</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4364138305832994</v>
+        <v>0.4490142767311477</v>
       </c>
       <c r="T70">
-        <v>2.723532494870455</v>
+        <v>2.81138838180176</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1683768712870503</v>
+        <v>0.1659366267756438</v>
       </c>
       <c r="W70">
-        <v>0.1669899242455603</v>
+        <v>0.1674799253434507</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5612562376235011</v>
+        <v>0.553122089252146</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2547555742736368</v>
+        <v>0.2563055742736368</v>
       </c>
       <c r="C71">
-        <v>0.01595684513975604</v>
+        <v>-0.03650132435429532</v>
       </c>
       <c r="D71">
-        <v>2.398156845139756</v>
+        <v>2.380498675645704</v>
       </c>
       <c r="E71">
-        <v>0.9511999999999998</v>
+        <v>0.986</v>
       </c>
       <c r="F71">
-        <v>2.4012</v>
+        <v>2.436</v>
       </c>
       <c r="G71">
         <v>0.019</v>
@@ -7231,37 +7231,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M71">
-        <v>0.48216096</v>
+        <v>0.4891488</v>
       </c>
       <c r="N71">
-        <v>-0.2154670824489796</v>
+        <v>-0.2224549224489796</v>
       </c>
       <c r="O71">
-        <v>-0.06464012473469387</v>
+        <v>-0.06673647673469386</v>
       </c>
       <c r="P71">
-        <v>-0.1508269577142857</v>
+        <v>-0.1557184457142857</v>
       </c>
       <c r="Q71">
-        <v>-0.08282695771428567</v>
+        <v>-0.08771844571428572</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4490142767311477</v>
+        <v>0.462454752622186</v>
       </c>
       <c r="T71">
-        <v>2.81138838180176</v>
+        <v>2.905101327861819</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1659366267756438</v>
+        <v>0.1635661035359917</v>
       </c>
       <c r="W71">
-        <v>0.1674799253434507</v>
+        <v>0.1679559264099729</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.553122089252146</v>
+        <v>0.5452203451199725</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2563055742736368</v>
+        <v>0.2578555742736368</v>
       </c>
       <c r="C72">
-        <v>-0.03650132435429532</v>
+        <v>-0.08870135243603672</v>
       </c>
       <c r="D72">
-        <v>2.380498675645704</v>
+        <v>2.363098647563963</v>
       </c>
       <c r="E72">
-        <v>0.986</v>
+        <v>1.0208</v>
       </c>
       <c r="F72">
-        <v>2.436</v>
+        <v>2.4708</v>
       </c>
       <c r="G72">
         <v>0.019</v>
@@ -7313,37 +7313,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M72">
-        <v>0.4891488</v>
+        <v>0.49613664</v>
       </c>
       <c r="N72">
-        <v>-0.2224549224489796</v>
+        <v>-0.2294427624489796</v>
       </c>
       <c r="O72">
-        <v>-0.06673647673469386</v>
+        <v>-0.06883282873469387</v>
       </c>
       <c r="P72">
-        <v>-0.1557184457142857</v>
+        <v>-0.1606099337142857</v>
       </c>
       <c r="Q72">
-        <v>-0.08771844571428572</v>
+        <v>-0.09260993371428572</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.462454752622186</v>
+        <v>0.4768221578850201</v>
       </c>
       <c r="T72">
-        <v>2.905101327861819</v>
+        <v>3.005277235719124</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1635661035359917</v>
+        <v>0.1612623555988651</v>
       </c>
       <c r="W72">
-        <v>0.1679559264099729</v>
+        <v>0.1684185189957479</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5452203451199725</v>
+        <v>0.5375411853295504</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2578555742736368</v>
+        <v>0.2594055742736368</v>
       </c>
       <c r="C73">
-        <v>-0.08870135243603539</v>
+        <v>-0.1406488586103452</v>
       </c>
       <c r="D73">
-        <v>2.363098647563964</v>
+        <v>2.345951141389654</v>
       </c>
       <c r="E73">
-        <v>1.0208</v>
+        <v>1.055599999999999</v>
       </c>
       <c r="F73">
-        <v>2.4708</v>
+        <v>2.505599999999999</v>
       </c>
       <c r="G73">
         <v>0.019</v>
@@ -7395,37 +7395,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M73">
-        <v>0.49613664</v>
+        <v>0.5031244799999999</v>
       </c>
       <c r="N73">
-        <v>-0.2294427624489795</v>
+        <v>-0.2364306024489795</v>
       </c>
       <c r="O73">
-        <v>-0.06883282873469386</v>
+        <v>-0.07092918073469383</v>
       </c>
       <c r="P73">
-        <v>-0.1606099337142857</v>
+        <v>-0.1655014217142856</v>
       </c>
       <c r="Q73">
-        <v>-0.09260993371428566</v>
+        <v>-0.09750142171428561</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4768221578850199</v>
+        <v>0.4922158063809136</v>
       </c>
       <c r="T73">
-        <v>3.005277235719122</v>
+        <v>3.112608565566235</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1612623555988651</v>
+        <v>0.159022600659992</v>
       </c>
       <c r="W73">
-        <v>0.1684185189957479</v>
+        <v>0.1688682617874736</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5375411853295504</v>
+        <v>0.5300753355333068</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2594055742736368</v>
+        <v>0.2609555742736368</v>
       </c>
       <c r="C74">
-        <v>-0.1406488586103452</v>
+        <v>-0.1923493004484422</v>
       </c>
       <c r="D74">
-        <v>2.345951141389654</v>
+        <v>2.329050699551557</v>
       </c>
       <c r="E74">
-        <v>1.055599999999999</v>
+        <v>1.0904</v>
       </c>
       <c r="F74">
-        <v>2.505599999999999</v>
+        <v>2.5404</v>
       </c>
       <c r="G74">
         <v>0.019</v>
@@ -7477,37 +7477,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M74">
-        <v>0.5031244799999999</v>
+        <v>0.51011232</v>
       </c>
       <c r="N74">
-        <v>-0.2364306024489795</v>
+        <v>-0.2434184424489795</v>
       </c>
       <c r="O74">
-        <v>-0.07092918073469383</v>
+        <v>-0.07302553273469385</v>
       </c>
       <c r="P74">
-        <v>-0.1655014217142856</v>
+        <v>-0.1703929097142857</v>
       </c>
       <c r="Q74">
-        <v>-0.09750142171428561</v>
+        <v>-0.1023929097142857</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4922158063809136</v>
+        <v>0.5087497251357621</v>
       </c>
       <c r="T74">
-        <v>3.112608565566235</v>
+        <v>3.227890364290909</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.159022600659992</v>
+        <v>0.1568442088701291</v>
       </c>
       <c r="W74">
-        <v>0.1688682617874736</v>
+        <v>0.1693056828588781</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5300753355333068</v>
+        <v>0.522814029567097</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2609555742736368</v>
+        <v>0.2625055742736367</v>
       </c>
       <c r="C75">
-        <v>-0.1923493004484422</v>
+        <v>-0.2438079793790839</v>
       </c>
       <c r="D75">
-        <v>2.329050699551557</v>
+        <v>2.312392020620916</v>
       </c>
       <c r="E75">
-        <v>1.0904</v>
+        <v>1.1252</v>
       </c>
       <c r="F75">
-        <v>2.5404</v>
+        <v>2.5752</v>
       </c>
       <c r="G75">
         <v>0.019</v>
@@ -7559,37 +7559,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M75">
-        <v>0.51011232</v>
+        <v>0.5171001599999999</v>
       </c>
       <c r="N75">
-        <v>-0.2434184424489795</v>
+        <v>-0.2504062824489795</v>
       </c>
       <c r="O75">
-        <v>-0.07302553273469385</v>
+        <v>-0.07512188473469385</v>
       </c>
       <c r="P75">
-        <v>-0.1703929097142857</v>
+        <v>-0.1752843977142857</v>
       </c>
       <c r="Q75">
-        <v>-0.1023929097142857</v>
+        <v>-0.1072843977142857</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5087497251357621</v>
+        <v>0.5265554837948299</v>
       </c>
       <c r="T75">
-        <v>3.227890364290909</v>
+        <v>3.352039993686714</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1568442088701291</v>
+        <v>0.1547246925340463</v>
       </c>
       <c r="W75">
-        <v>0.1693056828588781</v>
+        <v>0.1697312817391635</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.522814029567097</v>
+        <v>0.5157489751134876</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2625055742736367</v>
+        <v>0.2640555742736368</v>
       </c>
       <c r="C76">
-        <v>-0.2438079793790839</v>
+        <v>-0.2950300462330047</v>
       </c>
       <c r="D76">
-        <v>2.312392020620916</v>
+        <v>2.295969953766995</v>
       </c>
       <c r="E76">
-        <v>1.1252</v>
+        <v>1.159999999999999</v>
       </c>
       <c r="F76">
-        <v>2.5752</v>
+        <v>2.609999999999999</v>
       </c>
       <c r="G76">
         <v>0.019</v>
@@ -7641,37 +7641,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M76">
-        <v>0.5171001599999999</v>
+        <v>0.5240879999999999</v>
       </c>
       <c r="N76">
-        <v>-0.2504062824489795</v>
+        <v>-0.2573941224489795</v>
       </c>
       <c r="O76">
-        <v>-0.07512188473469385</v>
+        <v>-0.07721823673469384</v>
       </c>
       <c r="P76">
-        <v>-0.1752843977142857</v>
+        <v>-0.1801758857142856</v>
       </c>
       <c r="Q76">
-        <v>-0.1072843977142857</v>
+        <v>-0.1121758857142856</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5265554837948299</v>
+        <v>0.5457857031466231</v>
       </c>
       <c r="T76">
-        <v>3.352039993686714</v>
+        <v>3.486121593434182</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1547246925340463</v>
+        <v>0.1526616966335923</v>
       </c>
       <c r="W76">
-        <v>0.1697312817391635</v>
+        <v>0.1701455313159747</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5157489751134876</v>
+        <v>0.5088723221119744</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2640555742736368</v>
+        <v>0.2656055742736368</v>
       </c>
       <c r="C77">
-        <v>-0.2950300462330047</v>
+        <v>-0.3460205065527626</v>
       </c>
       <c r="D77">
-        <v>2.295969953766995</v>
+        <v>2.279779493447237</v>
       </c>
       <c r="E77">
-        <v>1.159999999999999</v>
+        <v>1.1948</v>
       </c>
       <c r="F77">
-        <v>2.609999999999999</v>
+        <v>2.6448</v>
       </c>
       <c r="G77">
         <v>0.019</v>
@@ -7723,37 +7723,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M77">
-        <v>0.5240879999999999</v>
+        <v>0.53107584</v>
       </c>
       <c r="N77">
-        <v>-0.2573941224489795</v>
+        <v>-0.2643819624489795</v>
       </c>
       <c r="O77">
-        <v>-0.07721823673469384</v>
+        <v>-0.07931458873469387</v>
       </c>
       <c r="P77">
-        <v>-0.1801758857142856</v>
+        <v>-0.1850673737142857</v>
       </c>
       <c r="Q77">
-        <v>-0.1121758857142856</v>
+        <v>-0.1170673737142857</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5457857031466231</v>
+        <v>0.5666184407777325</v>
       </c>
       <c r="T77">
-        <v>3.486121593434182</v>
+        <v>3.631376659827274</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1526616966335923</v>
+        <v>0.1506529900989398</v>
       </c>
       <c r="W77">
-        <v>0.1701455313159747</v>
+        <v>0.1705488795881329</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5088723221119744</v>
+        <v>0.5021766336631326</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2656055742736368</v>
+        <v>0.2965045330919159</v>
       </c>
       <c r="C78">
-        <v>-0.3460205065527626</v>
+        <v>-0.66179992010392</v>
       </c>
       <c r="D78">
-        <v>2.279779493447237</v>
+        <v>1.99880007989608</v>
       </c>
       <c r="E78">
-        <v>1.1948</v>
+        <v>1.2296</v>
       </c>
       <c r="F78">
-        <v>2.6448</v>
+        <v>2.6796</v>
       </c>
       <c r="G78">
         <v>0.019</v>
@@ -7805,45 +7805,45 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M78">
-        <v>0.53107584</v>
+        <v>0.63184968</v>
       </c>
       <c r="N78">
-        <v>-0.2643819624489795</v>
+        <v>-0.3651558024489795</v>
       </c>
       <c r="O78">
-        <v>-0.07931458873469387</v>
+        <v>-0.1095467407346939</v>
       </c>
       <c r="P78">
-        <v>-0.1850673737142857</v>
+        <v>-0.2556090617142857</v>
       </c>
       <c r="Q78">
-        <v>-0.1170673737142857</v>
+        <v>-0.1876090617142857</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5666184407777325</v>
+        <v>0.5996929765431951</v>
       </c>
       <c r="T78">
-        <v>3.631376659827274</v>
+        <v>3.861986960480166</v>
       </c>
       <c r="U78">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1506529900989398</v>
+        <v>0.1266253126302226</v>
       </c>
       <c r="W78">
-        <v>0.1705488795881329</v>
+        <v>0.2059417512817935</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.5021766336631326</v>
+        <v>0.4220843754340754</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2965045330919159</v>
+        <v>0.2984045330919159</v>
       </c>
       <c r="C79">
-        <v>-0.66179992010392</v>
+        <v>-0.7116341718860162</v>
       </c>
       <c r="D79">
-        <v>1.99880007989608</v>
+        <v>1.983765828113984</v>
       </c>
       <c r="E79">
-        <v>1.2296</v>
+        <v>1.2644</v>
       </c>
       <c r="F79">
-        <v>2.6796</v>
+        <v>2.7144</v>
       </c>
       <c r="G79">
         <v>0.019</v>
@@ -7887,37 +7887,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M79">
-        <v>0.63184968</v>
+        <v>0.64005552</v>
       </c>
       <c r="N79">
-        <v>-0.3651558024489795</v>
+        <v>-0.3733616424489796</v>
       </c>
       <c r="O79">
-        <v>-0.1095467407346939</v>
+        <v>-0.1120084927346939</v>
       </c>
       <c r="P79">
-        <v>-0.2556090617142857</v>
+        <v>-0.2613531497142857</v>
       </c>
       <c r="Q79">
-        <v>-0.1876090617142857</v>
+        <v>-0.1933531497142857</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5996929765431951</v>
+        <v>0.6248699300224313</v>
       </c>
       <c r="T79">
-        <v>3.861986960480166</v>
+        <v>4.037531822320174</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1266253126302226</v>
+        <v>0.1250019111862454</v>
       </c>
       <c r="W79">
-        <v>0.2059417512817935</v>
+        <v>0.2063245493422833</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4220843754340754</v>
+        <v>0.4166730372874847</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2984045330919159</v>
+        <v>0.3003045330919158</v>
       </c>
       <c r="C80">
-        <v>-0.7116341718860162</v>
+        <v>-0.7612439476791062</v>
       </c>
       <c r="D80">
-        <v>1.983765828113984</v>
+        <v>1.968956052320894</v>
       </c>
       <c r="E80">
-        <v>1.2644</v>
+        <v>1.2992</v>
       </c>
       <c r="F80">
-        <v>2.7144</v>
+        <v>2.7492</v>
       </c>
       <c r="G80">
         <v>0.019</v>
@@ -7969,37 +7969,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M80">
-        <v>0.64005552</v>
+        <v>0.6482613599999999</v>
       </c>
       <c r="N80">
-        <v>-0.3733616424489796</v>
+        <v>-0.3815674824489795</v>
       </c>
       <c r="O80">
-        <v>-0.1120084927346939</v>
+        <v>-0.1144702447346938</v>
       </c>
       <c r="P80">
-        <v>-0.2613531497142857</v>
+        <v>-0.2670972377142856</v>
       </c>
       <c r="Q80">
-        <v>-0.1933531497142857</v>
+        <v>-0.1990972377142856</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6248699300224313</v>
+        <v>0.6524446885949281</v>
       </c>
       <c r="T80">
-        <v>4.037531822320174</v>
+        <v>4.229795242430659</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1250019111862454</v>
+        <v>0.1234196085130018</v>
       </c>
       <c r="W80">
-        <v>0.2063245493422833</v>
+        <v>0.2066976563126342</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4166730372874847</v>
+        <v>0.4113986950433394</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3003045330919158</v>
+        <v>0.3022045330919159</v>
       </c>
       <c r="C81">
-        <v>-0.7612439476791062</v>
+        <v>-0.8106342376958149</v>
       </c>
       <c r="D81">
-        <v>1.968956052320894</v>
+        <v>1.954365762304185</v>
       </c>
       <c r="E81">
-        <v>1.2992</v>
+        <v>1.334</v>
       </c>
       <c r="F81">
-        <v>2.7492</v>
+        <v>2.784</v>
       </c>
       <c r="G81">
         <v>0.019</v>
@@ -8051,37 +8051,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M81">
-        <v>0.6482613599999999</v>
+        <v>0.6564672</v>
       </c>
       <c r="N81">
-        <v>-0.3815674824489795</v>
+        <v>-0.3897733224489796</v>
       </c>
       <c r="O81">
-        <v>-0.1144702447346938</v>
+        <v>-0.1169319967346939</v>
       </c>
       <c r="P81">
-        <v>-0.2670972377142856</v>
+        <v>-0.2728413257142858</v>
       </c>
       <c r="Q81">
-        <v>-0.1990972377142856</v>
+        <v>-0.2048413257142858</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6524446885949281</v>
+        <v>0.6827769230246744</v>
       </c>
       <c r="T81">
-        <v>4.229795242430659</v>
+        <v>4.441285004552191</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1234196085130018</v>
+        <v>0.1218768634065893</v>
       </c>
       <c r="W81">
-        <v>0.2066976563126342</v>
+        <v>0.2070614356087263</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4113986950433394</v>
+        <v>0.4062562113552975</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3022045330919159</v>
+        <v>0.3041045330919159</v>
       </c>
       <c r="C82">
-        <v>-0.8106342376958149</v>
+        <v>-0.8598098853235578</v>
       </c>
       <c r="D82">
-        <v>1.954365762304185</v>
+        <v>1.939990114676442</v>
       </c>
       <c r="E82">
-        <v>1.334</v>
+        <v>1.3688</v>
       </c>
       <c r="F82">
-        <v>2.784</v>
+        <v>2.8188</v>
       </c>
       <c r="G82">
         <v>0.019</v>
@@ -8133,37 +8133,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M82">
-        <v>0.6564672</v>
+        <v>0.66467304</v>
       </c>
       <c r="N82">
-        <v>-0.3897733224489796</v>
+        <v>-0.3979791624489796</v>
       </c>
       <c r="O82">
-        <v>-0.1169319967346939</v>
+        <v>-0.1193937487346939</v>
       </c>
       <c r="P82">
-        <v>-0.2728413257142858</v>
+        <v>-0.2785854137142857</v>
       </c>
       <c r="Q82">
-        <v>-0.2048413257142858</v>
+        <v>-0.2105854137142857</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6827769230246744</v>
+        <v>0.7163020242364994</v>
       </c>
       <c r="T82">
-        <v>4.441285004552191</v>
+        <v>4.675036846897044</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1218768634065893</v>
+        <v>0.12037221077194</v>
       </c>
       <c r="W82">
-        <v>0.2070614356087263</v>
+        <v>0.2074162326999766</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4062562113552975</v>
+        <v>0.4012407025731334</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3041045330919159</v>
+        <v>0.3060045330919159</v>
       </c>
       <c r="C83">
-        <v>-0.8598098853235578</v>
+        <v>-0.9087755924850971</v>
       </c>
       <c r="D83">
-        <v>1.939990114676442</v>
+        <v>1.925824407514903</v>
       </c>
       <c r="E83">
-        <v>1.3688</v>
+        <v>1.4036</v>
       </c>
       <c r="F83">
-        <v>2.8188</v>
+        <v>2.8536</v>
       </c>
       <c r="G83">
         <v>0.019</v>
@@ -8215,37 +8215,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M83">
-        <v>0.66467304</v>
+        <v>0.67287888</v>
       </c>
       <c r="N83">
-        <v>-0.3979791624489796</v>
+        <v>-0.4061850024489795</v>
       </c>
       <c r="O83">
-        <v>-0.1193937487346939</v>
+        <v>-0.1218555007346939</v>
       </c>
       <c r="P83">
-        <v>-0.2785854137142857</v>
+        <v>-0.2843295017142857</v>
       </c>
       <c r="Q83">
-        <v>-0.2105854137142857</v>
+        <v>-0.2163295017142857</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7163020242364994</v>
+        <v>0.7535521366940828</v>
       </c>
       <c r="T83">
-        <v>4.675036846897044</v>
+        <v>4.934761116169103</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.12037221077194</v>
+        <v>0.1189042569820383</v>
       </c>
       <c r="W83">
-        <v>0.2074162326999766</v>
+        <v>0.2077623762036354</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4012407025731334</v>
+        <v>0.3963475232734611</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3060045330919159</v>
+        <v>0.3079045330919159</v>
       </c>
       <c r="C84">
-        <v>-0.9087755924850971</v>
+        <v>-0.9575359247659405</v>
       </c>
       <c r="D84">
-        <v>1.925824407514903</v>
+        <v>1.911864075234059</v>
       </c>
       <c r="E84">
-        <v>1.4036</v>
+        <v>1.4384</v>
       </c>
       <c r="F84">
-        <v>2.8536</v>
+        <v>2.8884</v>
       </c>
       <c r="G84">
         <v>0.019</v>
@@ -8297,37 +8297,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M84">
-        <v>0.67287888</v>
+        <v>0.68108472</v>
       </c>
       <c r="N84">
-        <v>-0.4061850024489795</v>
+        <v>-0.4143908424489796</v>
       </c>
       <c r="O84">
-        <v>-0.1218555007346939</v>
+        <v>-0.1243172527346939</v>
       </c>
       <c r="P84">
-        <v>-0.2843295017142857</v>
+        <v>-0.2900735897142857</v>
       </c>
       <c r="Q84">
-        <v>-0.2163295017142857</v>
+        <v>-0.2220735897142857</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7535521366940828</v>
+        <v>0.7951846153231465</v>
       </c>
       <c r="T84">
-        <v>4.934761116169103</v>
+        <v>5.225041181826109</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1189042569820383</v>
+        <v>0.1174716755726162</v>
       </c>
       <c r="W84">
-        <v>0.2077623762036354</v>
+        <v>0.2081001788999771</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3963475232734611</v>
+        <v>0.3915722519087206</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3079045330919159</v>
+        <v>0.3098045330919159</v>
       </c>
       <c r="C85">
-        <v>-0.9575359247659405</v>
+        <v>-1.006095316320327</v>
       </c>
       <c r="D85">
-        <v>1.911864075234059</v>
+        <v>1.898104683679673</v>
       </c>
       <c r="E85">
-        <v>1.4384</v>
+        <v>1.4732</v>
       </c>
       <c r="F85">
-        <v>2.8884</v>
+        <v>2.9232</v>
       </c>
       <c r="G85">
         <v>0.019</v>
@@ -8379,37 +8379,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M85">
-        <v>0.68108472</v>
+        <v>0.68929056</v>
       </c>
       <c r="N85">
-        <v>-0.4143908424489796</v>
+        <v>-0.4225966824489796</v>
       </c>
       <c r="O85">
-        <v>-0.1243172527346939</v>
+        <v>-0.1267790047346939</v>
       </c>
       <c r="P85">
-        <v>-0.2900735897142857</v>
+        <v>-0.2958176777142857</v>
       </c>
       <c r="Q85">
-        <v>-0.2220735897142857</v>
+        <v>-0.2278176777142857</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7951846153231465</v>
+        <v>0.8420211537808434</v>
       </c>
       <c r="T85">
-        <v>5.225041181826109</v>
+        <v>5.551606255690242</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1174716755726162</v>
+        <v>0.1160732032443707</v>
       </c>
       <c r="W85">
-        <v>0.2081001788999771</v>
+        <v>0.2084299386749774</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3915722519087206</v>
+        <v>0.3869106774812359</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3098045330919159</v>
+        <v>0.3117045330919159</v>
       </c>
       <c r="C86">
-        <v>-1.006095316320327</v>
+        <v>-1.054458074566892</v>
       </c>
       <c r="D86">
-        <v>1.898104683679673</v>
+        <v>1.884541925433108</v>
       </c>
       <c r="E86">
-        <v>1.4732</v>
+        <v>1.508</v>
       </c>
       <c r="F86">
-        <v>2.9232</v>
+        <v>2.958</v>
       </c>
       <c r="G86">
         <v>0.019</v>
@@ -8461,37 +8461,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M86">
-        <v>0.6892905599999999</v>
+        <v>0.6974964</v>
       </c>
       <c r="N86">
-        <v>-0.4225966824489795</v>
+        <v>-0.4308025224489796</v>
       </c>
       <c r="O86">
-        <v>-0.1267790047346938</v>
+        <v>-0.1292407567346939</v>
       </c>
       <c r="P86">
-        <v>-0.2958176777142856</v>
+        <v>-0.3015617657142857</v>
       </c>
       <c r="Q86">
-        <v>-0.2278176777142856</v>
+        <v>-0.2335617657142857</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8420211537808429</v>
+        <v>0.895102564032899</v>
       </c>
       <c r="T86">
-        <v>5.551606255690238</v>
+        <v>5.92171333940292</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1160732032443708</v>
+        <v>0.1147076361473781</v>
       </c>
       <c r="W86">
-        <v>0.2084299386749774</v>
+        <v>0.2087519393964483</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3869106774812359</v>
+        <v>0.3823587871579271</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3117045330919159</v>
+        <v>0.3136045330919158</v>
       </c>
       <c r="C87">
-        <v>-1.054458074566892</v>
+        <v>-1.102628384684435</v>
       </c>
       <c r="D87">
-        <v>1.884541925433108</v>
+        <v>1.871171615315565</v>
       </c>
       <c r="E87">
-        <v>1.508</v>
+        <v>1.5428</v>
       </c>
       <c r="F87">
-        <v>2.958</v>
+        <v>2.992799999999999</v>
       </c>
       <c r="G87">
         <v>0.019</v>
@@ -8543,37 +8543,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M87">
-        <v>0.6974964</v>
+        <v>0.7057022399999999</v>
       </c>
       <c r="N87">
-        <v>-0.4308025224489796</v>
+        <v>-0.4390083624489795</v>
       </c>
       <c r="O87">
-        <v>-0.1292407567346939</v>
+        <v>-0.1317025087346939</v>
       </c>
       <c r="P87">
-        <v>-0.3015617657142857</v>
+        <v>-0.3073058537142856</v>
       </c>
       <c r="Q87">
-        <v>-0.2335617657142857</v>
+        <v>-0.2393058537142856</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.895102564032899</v>
+        <v>0.9557670328923917</v>
       </c>
       <c r="T87">
-        <v>5.92171333940292</v>
+        <v>6.344692863645986</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1147076361473781</v>
+        <v>0.1133738264247342</v>
       </c>
       <c r="W87">
-        <v>0.2087519393964483</v>
+        <v>0.2090664517290477</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3823587871579271</v>
+        <v>0.3779127547491141</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3136045330919158</v>
+        <v>0.3155045330919159</v>
       </c>
       <c r="C88">
-        <v>-1.102628384684435</v>
+        <v>-1.150610313917668</v>
       </c>
       <c r="D88">
-        <v>1.871171615315565</v>
+        <v>1.857989686082332</v>
       </c>
       <c r="E88">
-        <v>1.5428</v>
+        <v>1.5776</v>
       </c>
       <c r="F88">
-        <v>2.992799999999999</v>
+        <v>3.0276</v>
       </c>
       <c r="G88">
         <v>0.019</v>
@@ -8625,37 +8625,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M88">
-        <v>0.7057022399999999</v>
+        <v>0.7139080799999999</v>
       </c>
       <c r="N88">
-        <v>-0.4390083624489795</v>
+        <v>-0.4472142024489795</v>
       </c>
       <c r="O88">
-        <v>-0.1317025087346939</v>
+        <v>-0.1341642607346938</v>
       </c>
       <c r="P88">
-        <v>-0.3073058537142856</v>
+        <v>-0.3130499417142857</v>
       </c>
       <c r="Q88">
-        <v>-0.2393058537142856</v>
+        <v>-0.2450499417142857</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9557670328923917</v>
+        <v>1.025764496961038</v>
       </c>
       <c r="T88">
-        <v>6.344692863645986</v>
+        <v>6.832746160849524</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1133738264247342</v>
+        <v>0.1120706789945649</v>
       </c>
       <c r="W88">
-        <v>0.2090664517290477</v>
+        <v>0.2093737338930816</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3779127547491141</v>
+        <v>0.3735689299818828</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3155045330919159</v>
+        <v>0.3174045330919159</v>
       </c>
       <c r="C89">
-        <v>-1.150610313917668</v>
+        <v>-1.198407815702226</v>
       </c>
       <c r="D89">
-        <v>1.857989686082332</v>
+        <v>1.844992184297774</v>
       </c>
       <c r="E89">
-        <v>1.5776</v>
+        <v>1.6124</v>
       </c>
       <c r="F89">
-        <v>3.0276</v>
+        <v>3.0624</v>
       </c>
       <c r="G89">
         <v>0.019</v>
@@ -8707,37 +8707,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M89">
-        <v>0.7139080799999999</v>
+        <v>0.72211392</v>
       </c>
       <c r="N89">
-        <v>-0.4472142024489795</v>
+        <v>-0.4554200424489795</v>
       </c>
       <c r="O89">
-        <v>-0.1341642607346938</v>
+        <v>-0.1366260127346939</v>
       </c>
       <c r="P89">
-        <v>-0.3130499417142857</v>
+        <v>-0.3187940297142857</v>
       </c>
       <c r="Q89">
-        <v>-0.2450499417142857</v>
+        <v>-0.2507940297142857</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.025764496961038</v>
+        <v>1.107428205041124</v>
       </c>
       <c r="T89">
-        <v>6.832746160849524</v>
+        <v>7.402141674253651</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1120706789945649</v>
+        <v>0.1107971485514448</v>
       </c>
       <c r="W89">
-        <v>0.2093737338930816</v>
+        <v>0.2096740323715693</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3735689299818828</v>
+        <v>0.369323828504816</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3174045330919159</v>
+        <v>0.3193045330919159</v>
       </c>
       <c r="C90">
-        <v>-1.198407815702226</v>
+        <v>-1.246024733617761</v>
       </c>
       <c r="D90">
-        <v>1.844992184297774</v>
+        <v>1.832175266382239</v>
       </c>
       <c r="E90">
-        <v>1.6124</v>
+        <v>1.6472</v>
       </c>
       <c r="F90">
-        <v>3.0624</v>
+        <v>3.0972</v>
       </c>
       <c r="G90">
         <v>0.019</v>
@@ -8789,37 +8789,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M90">
-        <v>0.72211392</v>
+        <v>0.7303197599999999</v>
       </c>
       <c r="N90">
-        <v>-0.4554200424489795</v>
+        <v>-0.4636258824489795</v>
       </c>
       <c r="O90">
-        <v>-0.1366260127346939</v>
+        <v>-0.1390877647346938</v>
       </c>
       <c r="P90">
-        <v>-0.3187940297142857</v>
+        <v>-0.3245381177142856</v>
       </c>
       <c r="Q90">
-        <v>-0.2507940297142857</v>
+        <v>-0.2565381177142856</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.107428205041124</v>
+        <v>1.203939860044863</v>
       </c>
       <c r="T90">
-        <v>7.402141674253651</v>
+        <v>8.075063644640347</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1107971485514448</v>
+        <v>0.1095522367699679</v>
       </c>
       <c r="W90">
-        <v>0.2096740323715693</v>
+        <v>0.2099675825696416</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.369323828504816</v>
+        <v>0.3651741225665597</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3193045330919159</v>
+        <v>0.3212045330919159</v>
       </c>
       <c r="C91">
-        <v>-1.246024733617761</v>
+        <v>-1.293464805177383</v>
       </c>
       <c r="D91">
-        <v>1.832175266382239</v>
+        <v>1.819535194822616</v>
       </c>
       <c r="E91">
-        <v>1.6472</v>
+        <v>1.682</v>
       </c>
       <c r="F91">
-        <v>3.0972</v>
+        <v>3.132</v>
       </c>
       <c r="G91">
         <v>0.019</v>
@@ -8871,37 +8871,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M91">
-        <v>0.7303197599999999</v>
+        <v>0.7385256</v>
       </c>
       <c r="N91">
-        <v>-0.4636258824489795</v>
+        <v>-0.4718317224489796</v>
       </c>
       <c r="O91">
-        <v>-0.1390877647346938</v>
+        <v>-0.1415495167346939</v>
       </c>
       <c r="P91">
-        <v>-0.3245381177142856</v>
+        <v>-0.3302822057142857</v>
       </c>
       <c r="Q91">
-        <v>-0.2565381177142856</v>
+        <v>-0.2622822057142857</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.203939860044863</v>
+        <v>1.319753846049349</v>
       </c>
       <c r="T91">
-        <v>8.075063644640347</v>
+        <v>8.882570009104384</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1095522367699679</v>
+        <v>0.108334989694746</v>
       </c>
       <c r="W91">
-        <v>0.2099675825696416</v>
+        <v>0.2102546094299789</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3651741225665597</v>
+        <v>0.3611166323158201</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3212045330919159</v>
+        <v>0.3231045330919159</v>
       </c>
       <c r="C92">
-        <v>-1.293464805177383</v>
+        <v>-1.340731665461334</v>
       </c>
       <c r="D92">
-        <v>1.819535194822616</v>
+        <v>1.807068334538666</v>
       </c>
       <c r="E92">
-        <v>1.682</v>
+        <v>1.7168</v>
       </c>
       <c r="F92">
-        <v>3.132</v>
+        <v>3.1668</v>
       </c>
       <c r="G92">
         <v>0.019</v>
@@ -8953,37 +8953,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M92">
-        <v>0.7385256</v>
+        <v>0.74673144</v>
       </c>
       <c r="N92">
-        <v>-0.4718317224489796</v>
+        <v>-0.4800375624489796</v>
       </c>
       <c r="O92">
-        <v>-0.1415495167346939</v>
+        <v>-0.1440112687346939</v>
       </c>
       <c r="P92">
-        <v>-0.3302822057142857</v>
+        <v>-0.3360262937142857</v>
       </c>
       <c r="Q92">
-        <v>-0.2622822057142857</v>
+        <v>-0.2680262937142857</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.319753846049349</v>
+        <v>1.461304273388166</v>
       </c>
       <c r="T92">
-        <v>8.882570009104384</v>
+        <v>9.869522232338205</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.108334989694746</v>
+        <v>0.1071444953024961</v>
       </c>
       <c r="W92">
-        <v>0.2102546094299789</v>
+        <v>0.2105353280076714</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3611166323158201</v>
+        <v>0.3571483176749869</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3231045330919159</v>
+        <v>0.3250045330919159</v>
       </c>
       <c r="C93">
-        <v>-1.340731665461334</v>
+        <v>-1.387828850602283</v>
       </c>
       <c r="D93">
-        <v>1.807068334538666</v>
+        <v>1.794771149397717</v>
       </c>
       <c r="E93">
-        <v>1.7168</v>
+        <v>1.7516</v>
       </c>
       <c r="F93">
-        <v>3.1668</v>
+        <v>3.2016</v>
       </c>
       <c r="G93">
         <v>0.019</v>
@@ -9035,37 +9035,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M93">
-        <v>0.74673144</v>
+        <v>0.7549372799999999</v>
       </c>
       <c r="N93">
-        <v>-0.4800375624489796</v>
+        <v>-0.4882434024489795</v>
       </c>
       <c r="O93">
-        <v>-0.1440112687346939</v>
+        <v>-0.1464730207346938</v>
       </c>
       <c r="P93">
-        <v>-0.3360262937142857</v>
+        <v>-0.3417703817142856</v>
       </c>
       <c r="Q93">
-        <v>-0.2680262937142857</v>
+        <v>-0.2737703817142856</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.461304273388166</v>
+        <v>1.638242307561687</v>
       </c>
       <c r="T93">
-        <v>9.869522232338205</v>
+        <v>11.10321251138048</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1071444953024961</v>
+        <v>0.1059798812231211</v>
       </c>
       <c r="W93">
-        <v>0.2105353280076714</v>
+        <v>0.2108099440075881</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3571483176749869</v>
+        <v>0.3532662707437371</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3250045330919159</v>
+        <v>0.3269045330919159</v>
       </c>
       <c r="C94">
-        <v>-1.387828850602283</v>
+        <v>-1.43475980112929</v>
       </c>
       <c r="D94">
-        <v>1.794771149397717</v>
+        <v>1.782640198870709</v>
       </c>
       <c r="E94">
-        <v>1.7516</v>
+        <v>1.7864</v>
       </c>
       <c r="F94">
-        <v>3.2016</v>
+        <v>3.2364</v>
       </c>
       <c r="G94">
         <v>0.019</v>
@@ -9117,37 +9117,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M94">
-        <v>0.7549372799999999</v>
+        <v>0.76314312</v>
       </c>
       <c r="N94">
-        <v>-0.4882434024489795</v>
+        <v>-0.4964492424489795</v>
       </c>
       <c r="O94">
-        <v>-0.1464730207346938</v>
+        <v>-0.1489347727346939</v>
       </c>
       <c r="P94">
-        <v>-0.3417703817142856</v>
+        <v>-0.3475144697142857</v>
       </c>
       <c r="Q94">
-        <v>-0.2737703817142856</v>
+        <v>-0.2795144697142857</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.638242307561687</v>
+        <v>1.865734065784785</v>
       </c>
       <c r="T94">
-        <v>11.10321251138048</v>
+        <v>12.68938572729198</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1059798812231211</v>
+        <v>0.1048403126078187</v>
       </c>
       <c r="W94">
-        <v>0.2108099440075881</v>
+        <v>0.2110786542870763</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3532662707437371</v>
+        <v>0.3494677086927291</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3269045330919159</v>
+        <v>0.3288045330919158</v>
       </c>
       <c r="C95">
-        <v>-1.43475980112929</v>
+        <v>-1.481527865177064</v>
       </c>
       <c r="D95">
-        <v>1.782640198870709</v>
+        <v>1.770672134822936</v>
       </c>
       <c r="E95">
-        <v>1.7864</v>
+        <v>1.8212</v>
       </c>
       <c r="F95">
-        <v>3.2364</v>
+        <v>3.2712</v>
       </c>
       <c r="G95">
         <v>0.019</v>
@@ -9199,37 +9199,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M95">
-        <v>0.76314312</v>
+        <v>0.77134896</v>
       </c>
       <c r="N95">
-        <v>-0.4964492424489795</v>
+        <v>-0.5046550824489795</v>
       </c>
       <c r="O95">
-        <v>-0.1489347727346939</v>
+        <v>-0.1513965247346938</v>
       </c>
       <c r="P95">
-        <v>-0.3475144697142857</v>
+        <v>-0.3532585577142857</v>
       </c>
       <c r="Q95">
-        <v>-0.2795144697142857</v>
+        <v>-0.2852585577142857</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.865734065784785</v>
+        <v>2.169056410082249</v>
       </c>
       <c r="T95">
-        <v>12.68938572729198</v>
+        <v>14.80428334850732</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1048403126078187</v>
+        <v>0.1037249901332675</v>
       </c>
       <c r="W95">
-        <v>0.2110786542870763</v>
+        <v>0.2113416473265755</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3494677086927291</v>
+        <v>0.3457499671108917</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3288045330919158</v>
+        <v>0.3307045330919159</v>
       </c>
       <c r="C96">
-        <v>-1.481527865177064</v>
+        <v>-1.528136301566801</v>
       </c>
       <c r="D96">
-        <v>1.770672134822936</v>
+        <v>1.758863698433198</v>
       </c>
       <c r="E96">
-        <v>1.8212</v>
+        <v>1.856</v>
       </c>
       <c r="F96">
-        <v>3.2712</v>
+        <v>3.306</v>
       </c>
       <c r="G96">
         <v>0.019</v>
@@ -9281,37 +9281,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M96">
-        <v>0.77134896</v>
+        <v>0.7795548</v>
       </c>
       <c r="N96">
-        <v>-0.5046550824489795</v>
+        <v>-0.5128609224489795</v>
       </c>
       <c r="O96">
-        <v>-0.1513965247346938</v>
+        <v>-0.1538582767346938</v>
       </c>
       <c r="P96">
-        <v>-0.3532585577142857</v>
+        <v>-0.3590026457142856</v>
       </c>
       <c r="Q96">
-        <v>-0.2852585577142857</v>
+        <v>-0.2910026457142856</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.169056410082249</v>
+        <v>2.593707692098701</v>
       </c>
       <c r="T96">
-        <v>14.80428334850732</v>
+        <v>17.76514001820879</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1037249901332675</v>
+        <v>0.1026331481318647</v>
       </c>
       <c r="W96">
-        <v>0.2113416473265755</v>
+        <v>0.2115991036705063</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3457499671108917</v>
+        <v>0.3421104937728823</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3307045330919159</v>
+        <v>0.3326045330919158</v>
       </c>
       <c r="C97">
-        <v>-1.528136301566801</v>
+        <v>-1.574588282764574</v>
       </c>
       <c r="D97">
-        <v>1.758863698433198</v>
+        <v>1.747211717235426</v>
       </c>
       <c r="E97">
-        <v>1.856</v>
+        <v>1.8908</v>
       </c>
       <c r="F97">
-        <v>3.306</v>
+        <v>3.3408</v>
       </c>
       <c r="G97">
         <v>0.019</v>
@@ -9363,37 +9363,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M97">
-        <v>0.7795548</v>
+        <v>0.78776064</v>
       </c>
       <c r="N97">
-        <v>-0.5128609224489795</v>
+        <v>-0.5210667624489795</v>
       </c>
       <c r="O97">
-        <v>-0.1538582767346938</v>
+        <v>-0.1563200287346939</v>
       </c>
       <c r="P97">
-        <v>-0.3590026457142856</v>
+        <v>-0.3647467337142857</v>
       </c>
       <c r="Q97">
-        <v>-0.2910026457142856</v>
+        <v>-0.2967467337142857</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.593707692098701</v>
+        <v>3.230684615123377</v>
       </c>
       <c r="T97">
-        <v>17.76514001820879</v>
+        <v>22.20642502276099</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1026331481318647</v>
+        <v>0.1015640528388244</v>
       </c>
       <c r="W97">
-        <v>0.2115991036705063</v>
+        <v>0.2118511963406052</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3421104937728823</v>
+        <v>0.3385468427960814</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3326045330919158</v>
+        <v>0.3345045330919159</v>
       </c>
       <c r="C98">
-        <v>-1.574588282764574</v>
+        <v>-1.6208868977229</v>
       </c>
       <c r="D98">
-        <v>1.747211717235426</v>
+        <v>1.735713102277099</v>
       </c>
       <c r="E98">
-        <v>1.890799999999999</v>
+        <v>1.9256</v>
       </c>
       <c r="F98">
-        <v>3.340799999999999</v>
+        <v>3.375599999999999</v>
       </c>
       <c r="G98">
         <v>0.019</v>
@@ -9445,37 +9445,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M98">
-        <v>0.7877606399999999</v>
+        <v>0.7959664799999999</v>
       </c>
       <c r="N98">
-        <v>-0.5210667624489795</v>
+        <v>-0.5292726024489796</v>
       </c>
       <c r="O98">
-        <v>-0.1563200287346939</v>
+        <v>-0.1587817807346939</v>
       </c>
       <c r="P98">
-        <v>-0.3647467337142857</v>
+        <v>-0.3704908217142857</v>
       </c>
       <c r="Q98">
-        <v>-0.2967467337142857</v>
+        <v>-0.3024908217142857</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.230684615123369</v>
+        <v>4.292312820164493</v>
       </c>
       <c r="T98">
-        <v>22.20642502276094</v>
+        <v>29.60856669701458</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1015640528388244</v>
+        <v>0.1005170007477025</v>
       </c>
       <c r="W98">
-        <v>0.2118511963406052</v>
+        <v>0.2120980912236917</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3385468427960813</v>
+        <v>0.3350566691590083</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3345045330919159</v>
+        <v>0.3364045330919159</v>
       </c>
       <c r="C99">
-        <v>-1.6208868977229</v>
+        <v>-1.667035154610839</v>
       </c>
       <c r="D99">
-        <v>1.735713102277099</v>
+        <v>1.724364845389161</v>
       </c>
       <c r="E99">
-        <v>1.9256</v>
+        <v>1.9604</v>
       </c>
       <c r="F99">
-        <v>3.375599999999999</v>
+        <v>3.4104</v>
       </c>
       <c r="G99">
         <v>0.019</v>
@@ -9527,37 +9527,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M99">
-        <v>0.7959664799999999</v>
+        <v>0.8041723199999999</v>
       </c>
       <c r="N99">
-        <v>-0.5292726024489796</v>
+        <v>-0.5374784424489796</v>
       </c>
       <c r="O99">
-        <v>-0.1587817807346939</v>
+        <v>-0.1612435327346939</v>
       </c>
       <c r="P99">
-        <v>-0.3704908217142857</v>
+        <v>-0.3762349097142857</v>
       </c>
       <c r="Q99">
-        <v>-0.3024908217142857</v>
+        <v>-0.3082349097142857</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.292312820164493</v>
+        <v>6.415569230246739</v>
       </c>
       <c r="T99">
-        <v>29.60856669701458</v>
+        <v>44.41285004552187</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1005170007477025</v>
+        <v>0.0994913170666035</v>
       </c>
       <c r="W99">
-        <v>0.2120980912236917</v>
+        <v>0.2123399474356949</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3350566691590083</v>
+        <v>0.3316377235553449</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3364045330919159</v>
+        <v>0.3383045330919159</v>
       </c>
       <c r="C100">
-        <v>-1.667035154610839</v>
+        <v>-1.713035983437686</v>
       </c>
       <c r="D100">
-        <v>1.724364845389161</v>
+        <v>1.713164016562313</v>
       </c>
       <c r="E100">
-        <v>1.9604</v>
+        <v>1.995199999999999</v>
       </c>
       <c r="F100">
-        <v>3.4104</v>
+        <v>3.445199999999999</v>
       </c>
       <c r="G100">
         <v>0.019</v>
@@ -9609,37 +9609,37 @@
         <v>0.2666938775510204</v>
       </c>
       <c r="M100">
-        <v>0.8041723199999999</v>
+        <v>0.8123781599999998</v>
       </c>
       <c r="N100">
-        <v>-0.5374784424489796</v>
+        <v>-0.5456842824489794</v>
       </c>
       <c r="O100">
-        <v>-0.1612435327346939</v>
+        <v>-0.1637052847346938</v>
       </c>
       <c r="P100">
-        <v>-0.3762349097142857</v>
+        <v>-0.3819789977142856</v>
       </c>
       <c r="Q100">
-        <v>-0.3082349097142857</v>
+        <v>-0.3139789977142856</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.415569230246739</v>
+        <v>12.78533846049348</v>
       </c>
       <c r="T100">
-        <v>44.41285004552187</v>
+        <v>88.82570009104374</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0994913170666035</v>
+        <v>0.09848635426795094</v>
       </c>
       <c r="W100">
-        <v>0.2123399474356949</v>
+        <v>0.2125769176636172</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3316377235553449</v>
+        <v>0.3282878475598365</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3383045330919159</v>
-      </c>
-      <c r="C101">
-        <v>-1.713035983437686</v>
-      </c>
-      <c r="D101">
-        <v>1.713164016562313</v>
-      </c>
-      <c r="E101">
-        <v>1.995199999999999</v>
-      </c>
-      <c r="F101">
-        <v>3.445199999999999</v>
-      </c>
-      <c r="G101">
-        <v>0.019</v>
-      </c>
-      <c r="H101">
-        <v>2.03</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.3346938775510204</v>
-      </c>
-      <c r="K101">
-        <v>0.068</v>
-      </c>
-      <c r="L101">
-        <v>0.2666938775510204</v>
-      </c>
-      <c r="M101">
-        <v>0.8123781599999998</v>
-      </c>
-      <c r="N101">
-        <v>-0.5456842824489794</v>
-      </c>
-      <c r="O101">
-        <v>-0.1637052847346938</v>
-      </c>
-      <c r="P101">
-        <v>-0.3819789977142856</v>
-      </c>
-      <c r="Q101">
-        <v>-0.3139789977142856</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>12.78533846049348</v>
-      </c>
-      <c r="T101">
-        <v>88.82570009104374</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09848635426795094</v>
-      </c>
-      <c r="W101">
-        <v>0.2125769176636172</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3282878475598365</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
